--- a/output/exports/52w_high.xlsx
+++ b/output/exports/52w_high.xlsx
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="AO2" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP2" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AQ2" t="n">
         <v>-0.1860642598434397</v>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="AO3" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP3" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0.07027007800283061</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="AO4" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP4" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0.1334990530806877</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="AO5" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP5" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AQ5" t="n">
         <v>-0.1202894372010538</v>
@@ -1261,7 +1261,7 @@
         <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="AO6" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP6" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AQ6" t="n">
         <v>-0.206133018539621</v>
@@ -1415,7 +1415,7 @@
         <v>13</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="AO7" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP7" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AQ7" t="n">
         <v>-0.03697762763578034</v>
@@ -1569,7 +1569,7 @@
         <v>13</v>
       </c>
       <c r="AT7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP8" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0.04000019929846939</v>
@@ -1723,90 +1723,90 @@
         <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>760</v>
+        <v>518.2999877929688</v>
       </c>
       <c r="B9" t="n">
-        <v>812.7999877929688</v>
+        <v>519</v>
       </c>
       <c r="C9" t="n">
-        <v>743.0499877929688</v>
+        <v>498.2000122070312</v>
       </c>
       <c r="D9" t="n">
-        <v>804.9000244140625</v>
+        <v>514.6500244140625</v>
       </c>
       <c r="E9" t="n">
-        <v>4284956</v>
+        <v>700202</v>
       </c>
       <c r="F9" t="n">
-        <v>762.75</v>
+        <v>515.9500122070312</v>
       </c>
       <c r="G9" t="n">
-        <v>5.526060231276642</v>
+        <v>-0.251960027563114</v>
       </c>
       <c r="H9" t="n">
-        <v>757.5349975585938</v>
+        <v>477.7250015258789</v>
       </c>
       <c r="I9" t="n">
-        <v>656.758994140625</v>
+        <v>448.4090008544922</v>
       </c>
       <c r="J9" t="n">
-        <v>636.3507482910156</v>
+        <v>411.5989010620117</v>
       </c>
       <c r="K9" t="n">
-        <v>517.2344982910156</v>
+        <v>339.4084501647949</v>
       </c>
       <c r="L9" t="n">
-        <v>761.7559380815349</v>
+        <v>487.983619267182</v>
       </c>
       <c r="M9" t="n">
-        <v>740.304252556464</v>
+        <v>475.7971813859971</v>
       </c>
       <c r="N9" t="n">
-        <v>686.9536979892773</v>
+        <v>451.5887923519305</v>
       </c>
       <c r="O9" t="n">
-        <v>54.46686797716371</v>
+        <v>62.39882492748989</v>
       </c>
       <c r="P9" t="n">
-        <v>36.65714372907366</v>
+        <v>18.55357360839844</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.554248057795589</v>
+        <v>3.605085539347245</v>
       </c>
       <c r="R9" t="n">
-        <v>2119138.45</v>
+        <v>440852.2</v>
       </c>
       <c r="S9" t="n">
-        <v>2.022027395142587</v>
+        <v>1.588291949093143</v>
       </c>
       <c r="T9" t="n">
-        <v>812.7999877929688</v>
+        <v>519</v>
       </c>
       <c r="U9" t="n">
-        <v>262.6000061035156</v>
+        <v>212.5500030517578</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9719443279468255</v>
+        <v>-0.8381455849590559</v>
       </c>
       <c r="W9" t="n">
-        <v>206.5118071995683</v>
+        <v>142.1312712419678</v>
       </c>
       <c r="X9" t="n">
-        <v>55.61607492800982</v>
+        <v>51.63147062607943</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>717.2000122070312</v>
+        <v>441.2000122070312</v>
       </c>
       <c r="AA9" t="n">
-        <v>798.8499755859375</v>
+        <v>518</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1815,27 +1815,27 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>Near Breakout</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>NRBBEARING</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>TDPOWERSYS.NS</t>
+          <t>NRBBEARING.NS</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>TD Power Systems Limited</t>
+          <t>NRB Bearing Limited</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
@@ -1852,115 +1852,115 @@
       </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>52W High Watch</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP9" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.06898572389981884</v>
+        <v>0.04560891802842767</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Strong price trend | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Price is close to resistance | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS9" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="AT9" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1690</v>
+        <v>760</v>
       </c>
       <c r="B10" t="n">
-        <v>1795</v>
+        <v>812.7999877929688</v>
       </c>
       <c r="C10" t="n">
-        <v>1676.199951171875</v>
+        <v>743.0499877929688</v>
       </c>
       <c r="D10" t="n">
-        <v>1787.199951171875</v>
+        <v>804.9000244140625</v>
       </c>
       <c r="E10" t="n">
-        <v>254979</v>
+        <v>4284956</v>
       </c>
       <c r="F10" t="n">
-        <v>1706.699951171875</v>
+        <v>762.75</v>
       </c>
       <c r="G10" t="n">
-        <v>4.716704886803691</v>
+        <v>5.526060231276642</v>
       </c>
       <c r="H10" t="n">
-        <v>1611.504992675781</v>
+        <v>757.5349975585938</v>
       </c>
       <c r="I10" t="n">
-        <v>1546.695991210938</v>
+        <v>656.758994140625</v>
       </c>
       <c r="J10" t="n">
-        <v>1520.182996826172</v>
+        <v>636.3507482910156</v>
       </c>
       <c r="K10" t="n">
-        <v>1471.475498657227</v>
+        <v>517.2344982910156</v>
       </c>
       <c r="L10" t="n">
-        <v>1690.789820334797</v>
+        <v>761.7559380815349</v>
       </c>
       <c r="M10" t="n">
-        <v>1637.017601923169</v>
+        <v>740.304252556464</v>
       </c>
       <c r="N10" t="n">
-        <v>1569.703649057662</v>
+        <v>686.9536979892773</v>
       </c>
       <c r="O10" t="n">
-        <v>78.00239595985363</v>
+        <v>54.46686797716371</v>
       </c>
       <c r="P10" t="n">
-        <v>67.10716901506696</v>
+        <v>36.65714372907366</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.754877509428337</v>
+        <v>4.554248057795589</v>
       </c>
       <c r="R10" t="n">
-        <v>131176.35</v>
+        <v>2119138.45</v>
       </c>
       <c r="S10" t="n">
-        <v>1.943787885544917</v>
+        <v>2.022027395142587</v>
       </c>
       <c r="T10" t="n">
-        <v>1800</v>
+        <v>812.7999877929688</v>
       </c>
       <c r="U10" t="n">
-        <v>1165</v>
+        <v>262.6000061035156</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7111138237847222</v>
+        <v>-0.9719443279468255</v>
       </c>
       <c r="W10" t="n">
-        <v>53.40772113063304</v>
+        <v>206.5118071995683</v>
       </c>
       <c r="X10" t="n">
-        <v>21.456317336086</v>
+        <v>55.61607492800982</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1499</v>
+        <v>717.2000122070312</v>
       </c>
       <c r="AA10" t="n">
-        <v>1747.400024414062</v>
+        <v>798.8499755859375</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1979,17 +1979,17 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>VENKEYS</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>VENKEYS.NS</t>
+          <t>TDPOWERSYS.NS</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Venky's (India) Limited</t>
+          <t>TD Power Systems Limited</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -2014,107 +2014,107 @@
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP10" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.138098311939258</v>
+        <v>-0.06898572389981884</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>518.2999877929688</v>
+        <v>1690</v>
       </c>
       <c r="B11" t="n">
-        <v>519</v>
+        <v>1795</v>
       </c>
       <c r="C11" t="n">
-        <v>498.2000122070312</v>
+        <v>1676.199951171875</v>
       </c>
       <c r="D11" t="n">
-        <v>514.6500244140625</v>
+        <v>1787.199951171875</v>
       </c>
       <c r="E11" t="n">
-        <v>700202</v>
+        <v>254979</v>
       </c>
       <c r="F11" t="n">
-        <v>515.9500122070312</v>
+        <v>1706.699951171875</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.251960027563114</v>
+        <v>4.716704886803691</v>
       </c>
       <c r="H11" t="n">
-        <v>477.7250015258789</v>
+        <v>1611.504992675781</v>
       </c>
       <c r="I11" t="n">
-        <v>448.4090008544922</v>
+        <v>1546.695991210938</v>
       </c>
       <c r="J11" t="n">
-        <v>411.5989010620117</v>
+        <v>1520.182996826172</v>
       </c>
       <c r="K11" t="n">
-        <v>339.4084501647949</v>
+        <v>1471.475498657227</v>
       </c>
       <c r="L11" t="n">
-        <v>487.983619267182</v>
+        <v>1690.789820334797</v>
       </c>
       <c r="M11" t="n">
-        <v>475.7971813859971</v>
+        <v>1637.017601923169</v>
       </c>
       <c r="N11" t="n">
-        <v>451.5887923519305</v>
+        <v>1569.703649057662</v>
       </c>
       <c r="O11" t="n">
-        <v>62.39882492748989</v>
+        <v>78.00239595985363</v>
       </c>
       <c r="P11" t="n">
-        <v>18.55357360839844</v>
+        <v>67.10716901506696</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.605085539347245</v>
+        <v>3.754877509428337</v>
       </c>
       <c r="R11" t="n">
-        <v>440852.2</v>
+        <v>131176.35</v>
       </c>
       <c r="S11" t="n">
-        <v>1.588291949093143</v>
+        <v>1.943787885544917</v>
       </c>
       <c r="T11" t="n">
-        <v>519</v>
+        <v>1800</v>
       </c>
       <c r="U11" t="n">
-        <v>212.5500030517578</v>
+        <v>1165</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8381455849590559</v>
+        <v>-0.7111138237847222</v>
       </c>
       <c r="W11" t="n">
-        <v>142.1312712419678</v>
+        <v>53.40772113063304</v>
       </c>
       <c r="X11" t="n">
-        <v>51.63147062607943</v>
+        <v>21.456317336086</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>441.2000122070312</v>
+        <v>1499</v>
       </c>
       <c r="AA11" t="n">
-        <v>518</v>
+        <v>1747.400024414062</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2128,22 +2128,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Near Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>NRBBEARING</t>
+          <t>VENKEYS</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>NRBBEARING.NS</t>
+          <t>VENKEYS.NS</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>NRB Bearing Limited</t>
+          <t>Venky's (India) Limited</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr"/>
@@ -2160,115 +2160,115 @@
       </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>52W High Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP11" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.04560891802842767</v>
+        <v>-0.138098311939258</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Price is close to resistance | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS11" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="AT11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17.72999954223633</v>
+        <v>232.0299987792969</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>239.8000030517578</v>
       </c>
       <c r="C12" t="n">
-        <v>17.54000091552734</v>
+        <v>222.8399963378906</v>
       </c>
       <c r="D12" t="n">
-        <v>19.56999969482422</v>
+        <v>239.0700073242188</v>
       </c>
       <c r="E12" t="n">
-        <v>150749037</v>
+        <v>2135648</v>
       </c>
       <c r="F12" t="n">
-        <v>17.54000091552734</v>
+        <v>231.5399932861328</v>
       </c>
       <c r="G12" t="n">
-        <v>11.57353861652204</v>
+        <v>3.252144016770564</v>
       </c>
       <c r="H12" t="n">
-        <v>15.60450005531311</v>
+        <v>212.5780014038086</v>
       </c>
       <c r="I12" t="n">
-        <v>15.21620000839233</v>
+        <v>203.0944009399414</v>
       </c>
       <c r="J12" t="n">
-        <v>14.83810000419617</v>
+        <v>196.8363003540039</v>
       </c>
       <c r="K12" t="n">
-        <v>13.97445498466492</v>
+        <v>193.2455002593994</v>
       </c>
       <c r="L12" t="n">
-        <v>16.74106045500679</v>
+        <v>220.7534353211591</v>
       </c>
       <c r="M12" t="n">
-        <v>15.95635542117231</v>
+        <v>214.3502841536207</v>
       </c>
       <c r="N12" t="n">
-        <v>15.36097110076036</v>
+        <v>205.9145931895171</v>
       </c>
       <c r="O12" t="n">
-        <v>83.71334295705454</v>
+        <v>76.43997435056383</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8635715757097516</v>
+        <v>9.304285321916852</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.41273167693582</v>
+        <v>3.89186641438409</v>
       </c>
       <c r="R12" t="n">
-        <v>12998039.95</v>
+        <v>883570.75</v>
       </c>
       <c r="S12" t="n">
-        <v>11.5978284095057</v>
+        <v>2.417065073736314</v>
       </c>
       <c r="T12" t="n">
-        <v>20</v>
+        <v>240.8000030517578</v>
       </c>
       <c r="U12" t="n">
-        <v>10.19999980926514</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.150001525878906</v>
+        <v>-0.7184367548231365</v>
       </c>
       <c r="W12" t="n">
-        <v>91.86274569385652</v>
+        <v>58.8293918006212</v>
       </c>
       <c r="X12" t="n">
-        <v>40.04123750299858</v>
+        <v>23.7131043172067</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.10000038146973</v>
+        <v>197</v>
       </c>
       <c r="AA12" t="n">
-        <v>18</v>
+        <v>240.8000030517578</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2282,22 +2282,22 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>Near Breakout</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>KROSS</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>AHCL.NS</t>
+          <t>KROSS.NS</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Anlon Healthcare Limited</t>
+          <t>Kross Limited</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr"/>
@@ -2314,115 +2314,115 @@
       </c>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>52W High Watch</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.2870200899278381</v>
+        <v>0.04112183090928875</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS12" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="AT12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>853.8499755859375</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="B13" t="n">
-        <v>1024.5</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>835.0499877929688</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="D13" t="n">
-        <v>1002.799987792969</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="E13" t="n">
-        <v>16245056</v>
+        <v>150749037</v>
       </c>
       <c r="F13" t="n">
-        <v>853.8499755859375</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="G13" t="n">
-        <v>17.44451794412916</v>
+        <v>11.57353861652204</v>
       </c>
       <c r="H13" t="n">
-        <v>695.7974975585937</v>
+        <v>15.60450005531311</v>
       </c>
       <c r="I13" t="n">
-        <v>644.2329968261719</v>
+        <v>15.21620000839233</v>
       </c>
       <c r="J13" t="n">
-        <v>587.8264984130859</v>
+        <v>14.83810000419617</v>
       </c>
       <c r="K13" t="n">
-        <v>496.8880000305176</v>
+        <v>13.97445498466492</v>
       </c>
       <c r="L13" t="n">
-        <v>805.9068546404013</v>
+        <v>16.74106045500679</v>
       </c>
       <c r="M13" t="n">
-        <v>729.2174817078741</v>
+        <v>15.95635542117231</v>
       </c>
       <c r="N13" t="n">
-        <v>657.9695633891705</v>
+        <v>15.36097110076036</v>
       </c>
       <c r="O13" t="n">
-        <v>82.65092360615722</v>
+        <v>83.71334295705454</v>
       </c>
       <c r="P13" t="n">
-        <v>53.1678728376116</v>
+        <v>0.8635715757097516</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.301941911130964</v>
+        <v>4.41273167693582</v>
       </c>
       <c r="R13" t="n">
-        <v>3259520.55</v>
+        <v>12998039.95</v>
       </c>
       <c r="S13" t="n">
-        <v>4.983878994105437</v>
+        <v>11.5978284095057</v>
       </c>
       <c r="T13" t="n">
-        <v>1024.5</v>
+        <v>20</v>
       </c>
       <c r="U13" t="n">
-        <v>320</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.118107584873719</v>
+        <v>-2.150001525878906</v>
       </c>
       <c r="W13" t="n">
-        <v>213.3749961853027</v>
+        <v>91.86274569385652</v>
       </c>
       <c r="X13" t="n">
-        <v>101.8161009586425</v>
+        <v>40.04123750299858</v>
       </c>
       <c r="Y13" t="b">
         <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>611</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="AA13" t="n">
-        <v>869</v>
+        <v>18</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2441,17 +2441,17 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>RAYMOND.NS</t>
+          <t>AHCL.NS</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Raymond Limited</t>
+          <t>Anlon Healthcare Limited</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr"/>
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP13" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.3415007451803956</v>
+        <v>-0.2870200899278381</v>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
@@ -2493,90 +2493,90 @@
         <v>33</v>
       </c>
       <c r="AT13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>468.1499938964844</v>
+        <v>853.8499755859375</v>
       </c>
       <c r="B14" t="n">
-        <v>468.1499938964844</v>
+        <v>1024.5</v>
       </c>
       <c r="C14" t="n">
-        <v>443</v>
+        <v>835.0499877929688</v>
       </c>
       <c r="D14" t="n">
-        <v>468.1499938964844</v>
+        <v>1002.799987792969</v>
       </c>
       <c r="E14" t="n">
-        <v>2933978</v>
+        <v>16245056</v>
       </c>
       <c r="F14" t="n">
-        <v>445.8999938964844</v>
+        <v>853.8499755859375</v>
       </c>
       <c r="G14" t="n">
-        <v>4.989908119434805</v>
+        <v>17.44451794412916</v>
       </c>
       <c r="H14" t="n">
-        <v>363.0925018310547</v>
+        <v>695.7974975585937</v>
       </c>
       <c r="I14" t="n">
-        <v>313.6170001220703</v>
+        <v>644.2329968261719</v>
       </c>
       <c r="J14" t="n">
-        <v>239.0209999084473</v>
+        <v>587.8264984130859</v>
       </c>
       <c r="K14" t="n">
-        <v>186.3643997192383</v>
+        <v>496.8880000305176</v>
       </c>
       <c r="L14" t="n">
-        <v>413.6108795709933</v>
+        <v>805.9068546404013</v>
       </c>
       <c r="M14" t="n">
-        <v>375.6118771050868</v>
+        <v>729.2174817078741</v>
       </c>
       <c r="N14" t="n">
-        <v>318.9293348966037</v>
+        <v>657.9695633891705</v>
       </c>
       <c r="O14" t="n">
-        <v>85.28079628769122</v>
+        <v>82.65092360615722</v>
       </c>
       <c r="P14" t="n">
-        <v>21.36428833007812</v>
+        <v>53.1678728376116</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.563556255177933</v>
+        <v>5.301941911130964</v>
       </c>
       <c r="R14" t="n">
-        <v>1425162.5</v>
+        <v>3259520.55</v>
       </c>
       <c r="S14" t="n">
-        <v>2.058697166112636</v>
+        <v>4.983878994105437</v>
       </c>
       <c r="T14" t="n">
-        <v>468.1499938964844</v>
+        <v>1024.5</v>
       </c>
       <c r="U14" t="n">
-        <v>104.5599975585938</v>
+        <v>320</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-2.118107584873719</v>
       </c>
       <c r="W14" t="n">
-        <v>347.7333634539735</v>
+        <v>213.3749961853027</v>
       </c>
       <c r="X14" t="n">
-        <v>151.201406814693</v>
+        <v>101.8161009586425</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>292.1499938964844</v>
+        <v>611</v>
       </c>
       <c r="AA14" t="n">
-        <v>445.8999938964844</v>
+        <v>869</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2595,17 +2595,17 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>SETL.NS</t>
+          <t>RAYMOND.NS</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Standard Engineering Technology Limited</t>
+          <t>Raymond Limited</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr"/>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.1264204545454546</v>
+        <v>-0.3415007451803956</v>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
@@ -2647,90 +2647,90 @@
         <v>33</v>
       </c>
       <c r="AT14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2970</v>
+        <v>468.1499938964844</v>
       </c>
       <c r="B15" t="n">
-        <v>3022.5</v>
+        <v>468.1499938964844</v>
       </c>
       <c r="C15" t="n">
-        <v>2752</v>
+        <v>443</v>
       </c>
       <c r="D15" t="n">
-        <v>3022.5</v>
+        <v>468.1499938964844</v>
       </c>
       <c r="E15" t="n">
-        <v>47215</v>
+        <v>2933978</v>
       </c>
       <c r="F15" t="n">
-        <v>2878.60009765625</v>
+        <v>445.8999938964844</v>
       </c>
       <c r="G15" t="n">
-        <v>4.998954264641098</v>
+        <v>4.989908119434805</v>
       </c>
       <c r="H15" t="n">
-        <v>2310.955017089844</v>
+        <v>363.0925018310547</v>
       </c>
       <c r="I15" t="n">
-        <v>2251.334016113281</v>
+        <v>313.6170001220703</v>
       </c>
       <c r="J15" t="n">
-        <v>1875.339006347656</v>
+        <v>239.0209999084473</v>
       </c>
       <c r="K15" t="n">
-        <v>1570.6</v>
+        <v>186.3643997192383</v>
       </c>
       <c r="L15" t="n">
-        <v>2590.507522035552</v>
+        <v>413.6108795709933</v>
       </c>
       <c r="M15" t="n">
-        <v>2420.266135092586</v>
+        <v>375.6118771050868</v>
       </c>
       <c r="N15" t="n">
-        <v>2227.123717319627</v>
+        <v>318.9293348966037</v>
       </c>
       <c r="O15" t="n">
-        <v>92.17156285485734</v>
+        <v>85.28079628769122</v>
       </c>
       <c r="P15" t="n">
-        <v>138.7857142857143</v>
+        <v>21.36428833007812</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.591752333687817</v>
+        <v>4.563556255177933</v>
       </c>
       <c r="R15" t="n">
-        <v>10351.1</v>
+        <v>1425162.5</v>
       </c>
       <c r="S15" t="n">
-        <v>4.561350967530021</v>
+        <v>2.058697166112636</v>
       </c>
       <c r="T15" t="n">
-        <v>3022.5</v>
+        <v>468.1499938964844</v>
       </c>
       <c r="U15" t="n">
-        <v>1050</v>
+        <v>104.5599975585938</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>187.8571428571429</v>
+        <v>347.7333634539735</v>
       </c>
       <c r="X15" t="n">
-        <v>92.44237870877373</v>
+        <v>151.201406814693</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>2050</v>
+        <v>292.1499938964844</v>
       </c>
       <c r="AA15" t="n">
-        <v>2878.60009765625</v>
+        <v>445.8999938964844</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -2749,17 +2749,17 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>SPECTRUM</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>SPECTRUM.NS</t>
+          <t>SETL.NS</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Spectrum Electrical Industries Limited</t>
+          <t>Standard Engineering Technology Limited</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr"/>
@@ -2784,13 +2784,13 @@
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP15" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.1479690512532134</v>
+        <v>-0.1264204545454546</v>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
@@ -2801,90 +2801,90 @@
         <v>33</v>
       </c>
       <c r="AT15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36</v>
+        <v>2970</v>
       </c>
       <c r="B16" t="n">
-        <v>36.59999847412109</v>
+        <v>3022.5</v>
       </c>
       <c r="C16" t="n">
-        <v>35.56999969482422</v>
+        <v>2752</v>
       </c>
       <c r="D16" t="n">
-        <v>36.59999847412109</v>
+        <v>3022.5</v>
       </c>
       <c r="E16" t="n">
-        <v>5579818</v>
+        <v>47215</v>
       </c>
       <c r="F16" t="n">
-        <v>34.86000061035156</v>
+        <v>2878.60009765625</v>
       </c>
       <c r="G16" t="n">
-        <v>4.991387932600455</v>
+        <v>4.998954264641098</v>
       </c>
       <c r="H16" t="n">
-        <v>28.17200012207031</v>
+        <v>2310.955017089844</v>
       </c>
       <c r="I16" t="n">
-        <v>26.26219997406006</v>
+        <v>2251.334016113281</v>
       </c>
       <c r="J16" t="n">
-        <v>26.97650001525879</v>
+        <v>1875.339006347656</v>
       </c>
       <c r="K16" t="n">
-        <v>24.15945003509522</v>
+        <v>1570.6</v>
       </c>
       <c r="L16" t="n">
-        <v>31.83109622153241</v>
+        <v>2590.507522035552</v>
       </c>
       <c r="M16" t="n">
-        <v>29.34814961533383</v>
+        <v>2420.266135092586</v>
       </c>
       <c r="N16" t="n">
-        <v>27.40213096404273</v>
+        <v>2227.123717319627</v>
       </c>
       <c r="O16" t="n">
-        <v>88.39971956238938</v>
+        <v>92.17156285485734</v>
       </c>
       <c r="P16" t="n">
-        <v>1.430714198521205</v>
+        <v>138.7857142857143</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.909055350187586</v>
+        <v>4.591752333687817</v>
       </c>
       <c r="R16" t="n">
-        <v>2650478.9</v>
+        <v>10351.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2.105211250691337</v>
+        <v>4.561350967530021</v>
       </c>
       <c r="T16" t="n">
-        <v>36.59999847412109</v>
+        <v>3022.5</v>
       </c>
       <c r="U16" t="n">
-        <v>15.75</v>
+        <v>1050</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>132.3809426928323</v>
+        <v>187.8571428571429</v>
       </c>
       <c r="X16" t="n">
-        <v>51.49350842404989</v>
+        <v>92.44237870877373</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>24.60000038146973</v>
+        <v>2050</v>
       </c>
       <c r="AA16" t="n">
-        <v>34.86000061035156</v>
+        <v>2878.60009765625</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -2903,17 +2903,17 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>STLNETWORK</t>
+          <t>SPECTRUM</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>STLNETWORK.NS</t>
+          <t>SPECTRUM.NS</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>STL Networks Limited</t>
+          <t>Spectrum Electrical Industries Limited</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr"/>
@@ -2938,13 +2938,13 @@
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP16" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.1449998450278989</v>
+        <v>-0.1479690512532134</v>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
@@ -2955,90 +2955,90 @@
         <v>33</v>
       </c>
       <c r="AT16" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>364</v>
+        <v>36</v>
       </c>
       <c r="B17" t="n">
-        <v>396.2999877929688</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="C17" t="n">
-        <v>358.6000061035156</v>
+        <v>35.56999969482422</v>
       </c>
       <c r="D17" t="n">
-        <v>396.2999877929688</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="E17" t="n">
-        <v>133752</v>
+        <v>5579818</v>
       </c>
       <c r="F17" t="n">
-        <v>377.4500122070312</v>
+        <v>34.86000061035156</v>
       </c>
       <c r="G17" t="n">
-        <v>4.994032315886709</v>
+        <v>4.991387932600455</v>
       </c>
       <c r="H17" t="n">
-        <v>317.1599975585938</v>
+        <v>28.17200012207031</v>
       </c>
       <c r="I17" t="n">
-        <v>294.5729986572265</v>
+        <v>26.26219997406006</v>
       </c>
       <c r="J17" t="n">
-        <v>290.3307009887695</v>
+        <v>26.97650001525879</v>
       </c>
       <c r="K17" t="n">
-        <v>270.8759503936768</v>
+        <v>24.15945003509522</v>
       </c>
       <c r="L17" t="n">
-        <v>345.6171401411684</v>
+        <v>31.83109622153241</v>
       </c>
       <c r="M17" t="n">
-        <v>324.1412070880301</v>
+        <v>29.34814961533383</v>
       </c>
       <c r="N17" t="n">
-        <v>304.0954221442457</v>
+        <v>27.40213096404273</v>
       </c>
       <c r="O17" t="n">
-        <v>82.9577237163173</v>
+        <v>88.39971956238938</v>
       </c>
       <c r="P17" t="n">
-        <v>17.52499825613839</v>
+        <v>1.430714198521205</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.422154629309158</v>
+        <v>3.909055350187586</v>
       </c>
       <c r="R17" t="n">
-        <v>58619.45</v>
+        <v>2650478.9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.281700015950337</v>
+        <v>2.105211250691337</v>
       </c>
       <c r="T17" t="n">
-        <v>397</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="U17" t="n">
-        <v>195</v>
+        <v>15.75</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1763254929549748</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>103.2307629707532</v>
+        <v>132.3809426928323</v>
       </c>
       <c r="X17" t="n">
-        <v>46.30312776642125</v>
+        <v>51.49350842404989</v>
       </c>
       <c r="Y17" t="b">
         <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>284.4500122070312</v>
+        <v>24.60000038146973</v>
       </c>
       <c r="AA17" t="n">
-        <v>377.4500122070312</v>
+        <v>34.86000061035156</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -3057,17 +3057,17 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>VALIANTORG</t>
+          <t>STLNETWORK</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>VALIANTORG.NS</t>
+          <t>STLNETWORK.NS</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Valiant Organics Limited</t>
+          <t>STL Networks Limited</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr"/>
@@ -3092,13 +3092,13 @@
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP17" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.1685290987967586</v>
+        <v>-0.1449998450278989</v>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
@@ -3109,90 +3109,90 @@
         <v>33</v>
       </c>
       <c r="AT17" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>232.0299987792969</v>
+        <v>364</v>
       </c>
       <c r="B18" t="n">
-        <v>239.8000030517578</v>
+        <v>396.2999877929688</v>
       </c>
       <c r="C18" t="n">
-        <v>222.8399963378906</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="D18" t="n">
-        <v>239.0700073242188</v>
+        <v>396.2999877929688</v>
       </c>
       <c r="E18" t="n">
-        <v>2135648</v>
+        <v>133752</v>
       </c>
       <c r="F18" t="n">
-        <v>231.5399932861328</v>
+        <v>377.4500122070312</v>
       </c>
       <c r="G18" t="n">
-        <v>3.252144016770564</v>
+        <v>4.994032315886709</v>
       </c>
       <c r="H18" t="n">
-        <v>212.5780014038086</v>
+        <v>317.1599975585938</v>
       </c>
       <c r="I18" t="n">
-        <v>203.0944009399414</v>
+        <v>294.5729986572265</v>
       </c>
       <c r="J18" t="n">
-        <v>196.8363003540039</v>
+        <v>290.3307009887695</v>
       </c>
       <c r="K18" t="n">
-        <v>193.2455002593994</v>
+        <v>270.8759503936768</v>
       </c>
       <c r="L18" t="n">
-        <v>220.7534353211591</v>
+        <v>345.6171401411684</v>
       </c>
       <c r="M18" t="n">
-        <v>214.3502841536207</v>
+        <v>324.1412070880301</v>
       </c>
       <c r="N18" t="n">
-        <v>205.9145931895171</v>
+        <v>304.0954221442457</v>
       </c>
       <c r="O18" t="n">
-        <v>76.43997435056383</v>
+        <v>82.9577237163173</v>
       </c>
       <c r="P18" t="n">
-        <v>9.304285321916852</v>
+        <v>17.52499825613839</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.89186641438409</v>
+        <v>4.422154629309158</v>
       </c>
       <c r="R18" t="n">
-        <v>883570.75</v>
+        <v>58619.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.417065073736314</v>
+        <v>2.281700015950337</v>
       </c>
       <c r="T18" t="n">
-        <v>240.8000030517578</v>
+        <v>397</v>
       </c>
       <c r="U18" t="n">
-        <v>150.5200042724609</v>
+        <v>195</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7184367548231365</v>
+        <v>-0.1763254929549748</v>
       </c>
       <c r="W18" t="n">
-        <v>58.8293918006212</v>
+        <v>103.2307629707532</v>
       </c>
       <c r="X18" t="n">
-        <v>23.7131043172067</v>
+        <v>46.30312776642125</v>
       </c>
       <c r="Y18" t="b">
         <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>197</v>
+        <v>284.4500122070312</v>
       </c>
       <c r="AA18" t="n">
-        <v>240.8000030517578</v>
+        <v>377.4500122070312</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -3206,22 +3206,22 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Near Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>KROSS</t>
+          <t>VALIANTORG</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>KROSS.NS</t>
+          <t>VALIANTORG.NS</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Kross Limited</t>
+          <t>Valiant Organics Limited</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr"/>
@@ -3238,32 +3238,32 @@
       </c>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>52W High Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP18" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.04112183090928875</v>
+        <v>-0.1685290987967586</v>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS18" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="AT18" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP19" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.1478930944683908</v>
@@ -3417,7 +3417,7 @@
         <v>54</v>
       </c>
       <c r="AT19" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP20" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.1011613601073889</v>
@@ -3571,7 +3571,7 @@
         <v>54</v>
       </c>
       <c r="AT20" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP21" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ21" t="n">
         <v>-0.02595494449136814</v>
@@ -3725,7 +3725,7 @@
         <v>59</v>
       </c>
       <c r="AT21" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP22" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ22" t="n">
         <v>-0.03036922132176373</v>
@@ -3879,7 +3879,7 @@
         <v>59</v>
       </c>
       <c r="AT22" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP23" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.09871266242138327</v>
@@ -4033,7 +4033,7 @@
         <v>67</v>
       </c>
       <c r="AT23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP24" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.1366635564233045</v>
@@ -4187,94 +4187,94 @@
         <v>67</v>
       </c>
       <c r="AT24" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>417.8500061035156</v>
+        <v>1194.5</v>
       </c>
       <c r="B25" t="n">
-        <v>469</v>
+        <v>1240.199951171875</v>
       </c>
       <c r="C25" t="n">
-        <v>414.5499877929688</v>
+        <v>1167.699951171875</v>
       </c>
       <c r="D25" t="n">
-        <v>463.4500122070312</v>
+        <v>1224.400024414062</v>
       </c>
       <c r="E25" t="n">
-        <v>10401534</v>
+        <v>113105</v>
       </c>
       <c r="F25" t="n">
-        <v>417.4500122070312</v>
+        <v>1194.5</v>
       </c>
       <c r="G25" t="n">
-        <v>11.01928342433169</v>
+        <v>2.503141432738598</v>
       </c>
       <c r="H25" t="n">
-        <v>376.9125015258789</v>
+        <v>1108.195007324219</v>
       </c>
       <c r="I25" t="n">
-        <v>381.5609997558594</v>
+        <v>990.9890014648438</v>
       </c>
       <c r="J25" t="n">
-        <v>385.7770001220703</v>
+        <v>960.7654998779296</v>
       </c>
       <c r="K25" t="n">
-        <v>368.4205001831054</v>
+        <v>953.6612490844726</v>
       </c>
       <c r="L25" t="n">
-        <v>406.932875731272</v>
+        <v>1178.257492178097</v>
       </c>
       <c r="M25" t="n">
-        <v>389.1526744553819</v>
+        <v>1120.807668877607</v>
       </c>
       <c r="N25" t="n">
-        <v>382.3194672036209</v>
+        <v>1033.789242859023</v>
       </c>
       <c r="O25" t="n">
-        <v>91.94474483361198</v>
+        <v>73.7586043348856</v>
       </c>
       <c r="P25" t="n">
-        <v>20.04643249511719</v>
+        <v>57.80355834960938</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.325478901090652</v>
+        <v>4.720970042227115</v>
       </c>
       <c r="R25" t="n">
-        <v>926456.55</v>
+        <v>115434.8</v>
       </c>
       <c r="S25" t="n">
-        <v>11.22722269058382</v>
+        <v>0.9798171781819693</v>
       </c>
       <c r="T25" t="n">
-        <v>469</v>
+        <v>1240.199951171875</v>
       </c>
       <c r="U25" t="n">
-        <v>242.25</v>
+        <v>855.2999877929688</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.183366267157516</v>
+        <v>-1.273982210923571</v>
       </c>
       <c r="W25" t="n">
-        <v>91.31063455398606</v>
+        <v>43.15445362901571</v>
       </c>
       <c r="X25" t="n">
-        <v>25.79376337003397</v>
+        <v>28.38940720192864</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>349.25</v>
+        <v>921</v>
       </c>
       <c r="AA25" t="n">
-        <v>444</v>
+        <v>1222</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Uptrend</t>
+          <t>Strong Uptrend</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4284,22 +4284,22 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>Breakout - Volume Confirmation Required</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>SMSPHARMA</t>
+          <t>HATSUN</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>SMSPHARMA.NS</t>
+          <t>HATSUN.NS</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>SMS Pharmaceuticals Limited</t>
+          <t>Hatsun Agro Product Limited</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr"/>
@@ -4316,29 +4316,29 @@
       </c>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>52W High Watch</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP25" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-0.1703153251137194</v>
+        <v>-0.007910429205460735</v>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS25" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="AT25" t="n">
         <v>67</v>
@@ -4346,85 +4346,85 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1194.5</v>
+        <v>788</v>
       </c>
       <c r="B26" t="n">
-        <v>1240.199951171875</v>
+        <v>832.4500122070312</v>
       </c>
       <c r="C26" t="n">
-        <v>1167.699951171875</v>
+        <v>776.5</v>
       </c>
       <c r="D26" t="n">
-        <v>1224.400024414062</v>
+        <v>832.4500122070312</v>
       </c>
       <c r="E26" t="n">
-        <v>113105</v>
+        <v>366669</v>
       </c>
       <c r="F26" t="n">
-        <v>1194.5</v>
+        <v>792.8499755859375</v>
       </c>
       <c r="G26" t="n">
-        <v>2.503141432738598</v>
+        <v>4.994644364065004</v>
       </c>
       <c r="H26" t="n">
-        <v>1108.195007324219</v>
+        <v>735.0150024414063</v>
       </c>
       <c r="I26" t="n">
-        <v>990.9890014648438</v>
+        <v>654.5690002441406</v>
       </c>
       <c r="J26" t="n">
-        <v>960.7654998779296</v>
+        <v>534.4489994812012</v>
       </c>
       <c r="K26" t="n">
-        <v>953.6612490844726</v>
+        <v>357.2836002349853</v>
       </c>
       <c r="L26" t="n">
-        <v>1178.257492178097</v>
+        <v>776.2103412453457</v>
       </c>
       <c r="M26" t="n">
-        <v>1120.807668877607</v>
+        <v>742.9510978583669</v>
       </c>
       <c r="N26" t="n">
-        <v>1033.789242859023</v>
+        <v>663.8059184870033</v>
       </c>
       <c r="O26" t="n">
-        <v>73.7586043348856</v>
+        <v>77.36057119285185</v>
       </c>
       <c r="P26" t="n">
-        <v>57.80355834960938</v>
+        <v>39.47858101981027</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.720970042227115</v>
+        <v>4.742456656964034</v>
       </c>
       <c r="R26" t="n">
-        <v>115434.8</v>
+        <v>319067.35</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9798171781819693</v>
+        <v>1.1491899750946</v>
       </c>
       <c r="T26" t="n">
-        <v>1240.199951171875</v>
+        <v>832.4500122070312</v>
       </c>
       <c r="U26" t="n">
-        <v>855.2999877929688</v>
+        <v>140.1000061035156</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.273982210923571</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>43.15445362901571</v>
+        <v>494.182709451104</v>
       </c>
       <c r="X26" t="n">
-        <v>28.38940720192864</v>
+        <v>132.9941849162763</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>921</v>
+        <v>622</v>
       </c>
       <c r="AA26" t="n">
-        <v>1222</v>
+        <v>801</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
@@ -4443,17 +4443,17 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>HATSUN</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>HATSUN.NS</t>
+          <t>SIGMAADV.NS</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>Hatsun Agro Product Limited</t>
+          <t>SIGMA ADVANCED SYSTEMS LIMITED</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr"/>
@@ -4478,13 +4478,13 @@
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP26" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-0.007910429205460735</v>
+        <v>-0.1494417219424637</v>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
@@ -4495,90 +4495,90 @@
         <v>86</v>
       </c>
       <c r="AT26" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>788</v>
+        <v>707.2000122070312</v>
       </c>
       <c r="B27" t="n">
-        <v>832.4500122070312</v>
+        <v>759.5499877929688</v>
       </c>
       <c r="C27" t="n">
-        <v>776.5</v>
+        <v>697.4000244140625</v>
       </c>
       <c r="D27" t="n">
-        <v>832.4500122070312</v>
+        <v>749.1500244140625</v>
       </c>
       <c r="E27" t="n">
-        <v>366669</v>
+        <v>1159874</v>
       </c>
       <c r="F27" t="n">
-        <v>792.8499755859375</v>
+        <v>707.25</v>
       </c>
       <c r="G27" t="n">
-        <v>4.994644364065004</v>
+        <v>5.924358347693537</v>
       </c>
       <c r="H27" t="n">
-        <v>735.0150024414063</v>
+        <v>635.3399978637696</v>
       </c>
       <c r="I27" t="n">
-        <v>654.5690002441406</v>
+        <v>575.095</v>
       </c>
       <c r="J27" t="n">
-        <v>534.4489994812012</v>
+        <v>561.7759991455079</v>
       </c>
       <c r="K27" t="n">
-        <v>357.2836002349853</v>
+        <v>535.4977503967285</v>
       </c>
       <c r="L27" t="n">
-        <v>776.2103412453457</v>
+        <v>685.294429763832</v>
       </c>
       <c r="M27" t="n">
-        <v>742.9510978583669</v>
+        <v>643.3756499259839</v>
       </c>
       <c r="N27" t="n">
-        <v>663.8059184870033</v>
+        <v>596.0650332218083</v>
       </c>
       <c r="O27" t="n">
-        <v>77.36057119285185</v>
+        <v>79.37362159475663</v>
       </c>
       <c r="P27" t="n">
-        <v>39.47858101981027</v>
+        <v>35.15000261579241</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.742456656964034</v>
+        <v>4.691984445076206</v>
       </c>
       <c r="R27" t="n">
-        <v>319067.35</v>
+        <v>918755.35</v>
       </c>
       <c r="S27" t="n">
-        <v>1.1491899750946</v>
+        <v>1.262440539802027</v>
       </c>
       <c r="T27" t="n">
-        <v>832.4500122070312</v>
+        <v>759.5499877929688</v>
       </c>
       <c r="U27" t="n">
-        <v>140.1000061035156</v>
+        <v>422</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>-1.369226982561808</v>
       </c>
       <c r="W27" t="n">
-        <v>494.182709451104</v>
+        <v>77.52370246778733</v>
       </c>
       <c r="X27" t="n">
-        <v>132.9941849162763</v>
+        <v>39.89788451194196</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>622</v>
+        <v>501.9500122070312</v>
       </c>
       <c r="AA27" t="n">
-        <v>801</v>
+        <v>749.7999877929688</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
@@ -4592,22 +4592,22 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Breakout - Volume Confirmation Required</t>
+          <t>Near Breakout</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>SOLARA</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>SIGMAADV.NS</t>
+          <t>SOLARA.NS</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>SIGMA ADVANCED SYSTEMS LIMITED</t>
+          <t>Solara Active Pharma Sciences Limited</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr"/>
@@ -4632,107 +4632,107 @@
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP27" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AQ27" t="n">
-        <v>-0.1494417219424637</v>
+        <v>0.00262930156476652</v>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS27" t="n">
         <v>86</v>
       </c>
       <c r="AT27" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>707.2000122070312</v>
+        <v>2705</v>
       </c>
       <c r="B28" t="n">
-        <v>759.5499877929688</v>
+        <v>2742</v>
       </c>
       <c r="C28" t="n">
-        <v>697.4000244140625</v>
+        <v>2662.800048828125</v>
       </c>
       <c r="D28" t="n">
-        <v>749.1500244140625</v>
+        <v>2727.89990234375</v>
       </c>
       <c r="E28" t="n">
-        <v>1159874</v>
+        <v>20275</v>
       </c>
       <c r="F28" t="n">
-        <v>707.25</v>
+        <v>2662.800048828125</v>
       </c>
       <c r="G28" t="n">
-        <v>5.924358347693537</v>
+        <v>2.444789406710246</v>
       </c>
       <c r="H28" t="n">
-        <v>635.3399978637696</v>
+        <v>2446.129992675781</v>
       </c>
       <c r="I28" t="n">
-        <v>575.095</v>
+        <v>2412.778002929687</v>
       </c>
       <c r="J28" t="n">
-        <v>561.7759991455079</v>
+        <v>2198.835006103516</v>
       </c>
       <c r="K28" t="n">
-        <v>535.4977503967285</v>
+        <v>1941.61799987793</v>
       </c>
       <c r="L28" t="n">
-        <v>685.294429763832</v>
+        <v>2559.806784359547</v>
       </c>
       <c r="M28" t="n">
-        <v>643.3756499259839</v>
+        <v>2495.231789366066</v>
       </c>
       <c r="N28" t="n">
-        <v>596.0650332218083</v>
+        <v>2395.51885712167</v>
       </c>
       <c r="O28" t="n">
-        <v>79.37362159475663</v>
+        <v>79.83733118661621</v>
       </c>
       <c r="P28" t="n">
-        <v>35.15000261579241</v>
+        <v>123.7428327287946</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.691984445076206</v>
+        <v>4.536194037855919</v>
       </c>
       <c r="R28" t="n">
-        <v>918755.35</v>
+        <v>24608.35</v>
       </c>
       <c r="S28" t="n">
-        <v>1.262440539802027</v>
+        <v>0.8239073322672995</v>
       </c>
       <c r="T28" t="n">
-        <v>759.5499877929688</v>
+        <v>2750</v>
       </c>
       <c r="U28" t="n">
-        <v>422</v>
+        <v>523.5</v>
       </c>
       <c r="V28" t="n">
-        <v>-1.369226982561808</v>
+        <v>-0.8036399147727272</v>
       </c>
       <c r="W28" t="n">
-        <v>77.52370246778733</v>
+        <v>421.0888065604107</v>
       </c>
       <c r="X28" t="n">
-        <v>39.89788451194196</v>
+        <v>40.49622029231571</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>501.9500122070312</v>
+        <v>2280</v>
       </c>
       <c r="AA28" t="n">
-        <v>749.7999877929688</v>
+        <v>2710</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
@@ -4746,22 +4746,22 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Near Breakout</t>
+          <t>Breakout - Volume Confirmation Required</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>SOLARA</t>
+          <t>SWANDEF</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>SOLARA.NS</t>
+          <t>SWANDEF.NS</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Limited</t>
+          <t>Swan Defence and Heavy Industries Limited</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr"/>
@@ -4786,107 +4786,107 @@
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP28" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.00262930156476652</v>
+        <v>-0.03996406842261901</v>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS28" t="n">
         <v>86</v>
       </c>
       <c r="AT28" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2705</v>
+        <v>118.5599975585938</v>
       </c>
       <c r="B29" t="n">
-        <v>2742</v>
+        <v>129.8999938964844</v>
       </c>
       <c r="C29" t="n">
-        <v>2662.800048828125</v>
+        <v>118.5599975585938</v>
       </c>
       <c r="D29" t="n">
-        <v>2727.89990234375</v>
+        <v>127.9100036621094</v>
       </c>
       <c r="E29" t="n">
-        <v>20275</v>
+        <v>234978</v>
       </c>
       <c r="F29" t="n">
-        <v>2662.800048828125</v>
+        <v>124.8000030517578</v>
       </c>
       <c r="G29" t="n">
-        <v>2.444789406710246</v>
+        <v>2.491987607613888</v>
       </c>
       <c r="H29" t="n">
-        <v>2446.129992675781</v>
+        <v>101.7580001831055</v>
       </c>
       <c r="I29" t="n">
-        <v>2412.778002929687</v>
+        <v>79.15080017089844</v>
       </c>
       <c r="J29" t="n">
-        <v>2198.835006103516</v>
+        <v>76.50930015563965</v>
       </c>
       <c r="K29" t="n">
-        <v>1941.61799987793</v>
+        <v>69.44295000076293</v>
       </c>
       <c r="L29" t="n">
-        <v>2559.806784359547</v>
+        <v>113.0802126330343</v>
       </c>
       <c r="M29" t="n">
-        <v>2495.231789366066</v>
+        <v>101.9796392248448</v>
       </c>
       <c r="N29" t="n">
-        <v>2395.51885712167</v>
+        <v>87.09472845403407</v>
       </c>
       <c r="O29" t="n">
-        <v>79.83733118661621</v>
+        <v>74.82636036992722</v>
       </c>
       <c r="P29" t="n">
-        <v>123.7428327287946</v>
+        <v>6.819999694824219</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.536194037855919</v>
+        <v>5.331873582648094</v>
       </c>
       <c r="R29" t="n">
-        <v>24608.35</v>
+        <v>258050.1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.8239073322672995</v>
+        <v>0.9105906178683907</v>
       </c>
       <c r="T29" t="n">
-        <v>2750</v>
+        <v>129.8999938964844</v>
       </c>
       <c r="U29" t="n">
-        <v>523.5</v>
+        <v>49.5099983215332</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.8036399147727272</v>
+        <v>-1.531940206218021</v>
       </c>
       <c r="W29" t="n">
-        <v>421.0888065604107</v>
+        <v>158.3518642667333</v>
       </c>
       <c r="X29" t="n">
-        <v>40.49622029231571</v>
+        <v>84.19436913423766</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>2280</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="AA29" t="n">
-        <v>2710</v>
+        <v>125.8199996948242</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
@@ -4905,17 +4905,17 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>SWANDEF</t>
+          <t>VALIANTLAB</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>SWANDEF.NS</t>
+          <t>VALIANTLAB.NS</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>Swan Defence and Heavy Industries Limited</t>
+          <t>Valiant Laboratories Limited</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr"/>
@@ -4940,13 +4940,13 @@
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP29" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AQ29" t="n">
-        <v>-0.03996406842261901</v>
+        <v>-0.04229064593422944</v>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
@@ -4957,90 +4957,90 @@
         <v>86</v>
       </c>
       <c r="AT29" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118.5599975585938</v>
+        <v>1085.699951171875</v>
       </c>
       <c r="B30" t="n">
-        <v>129.8999938964844</v>
+        <v>1124.849975585938</v>
       </c>
       <c r="C30" t="n">
-        <v>118.5599975585938</v>
+        <v>1060.550048828125</v>
       </c>
       <c r="D30" t="n">
-        <v>127.9100036621094</v>
+        <v>1113.75</v>
       </c>
       <c r="E30" t="n">
-        <v>234978</v>
+        <v>35432</v>
       </c>
       <c r="F30" t="n">
-        <v>124.8000030517578</v>
+        <v>1085.699951171875</v>
       </c>
       <c r="G30" t="n">
-        <v>2.491987607613888</v>
+        <v>2.583591239720384</v>
       </c>
       <c r="H30" t="n">
-        <v>101.7580001831055</v>
+        <v>969.1599914550782</v>
       </c>
       <c r="I30" t="n">
-        <v>79.15080017089844</v>
+        <v>839.0899963378906</v>
       </c>
       <c r="J30" t="n">
-        <v>76.50930015563965</v>
+        <v>773.2919989013672</v>
       </c>
       <c r="K30" t="n">
-        <v>69.44295000076293</v>
+        <v>775.4384997558594</v>
       </c>
       <c r="L30" t="n">
-        <v>113.0802126330343</v>
+        <v>1035.996071624864</v>
       </c>
       <c r="M30" t="n">
-        <v>101.9796392248448</v>
+        <v>973.217043701645</v>
       </c>
       <c r="N30" t="n">
-        <v>87.09472845403407</v>
+        <v>876.4770778251901</v>
       </c>
       <c r="O30" t="n">
-        <v>74.82636036992722</v>
+        <v>75.3699587091405</v>
       </c>
       <c r="P30" t="n">
-        <v>6.819999694824219</v>
+        <v>51.38927786690848</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.331873582648094</v>
+        <v>4.614076576153399</v>
       </c>
       <c r="R30" t="n">
-        <v>258050.1</v>
+        <v>29114.65</v>
       </c>
       <c r="S30" t="n">
-        <v>0.9105906178683907</v>
+        <v>1.216981828735705</v>
       </c>
       <c r="T30" t="n">
-        <v>129.8999938964844</v>
+        <v>1134.699951171875</v>
       </c>
       <c r="U30" t="n">
-        <v>49.5099983215332</v>
+        <v>584.0999755859375</v>
       </c>
       <c r="V30" t="n">
-        <v>-1.531940206218021</v>
+        <v>-1.846298763848424</v>
       </c>
       <c r="W30" t="n">
-        <v>158.3518642667333</v>
+        <v>90.67797407160414</v>
       </c>
       <c r="X30" t="n">
-        <v>84.19436913423766</v>
+        <v>43.62841158269227</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>78.48999786376953</v>
+        <v>812</v>
       </c>
       <c r="AA30" t="n">
-        <v>125.8199996948242</v>
+        <v>1134.699951171875</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
@@ -5054,22 +5054,22 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Breakout - Volume Confirmation Required</t>
+          <t>Near Breakout</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>VALIANTLAB</t>
+          <t>YUKEN</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>VALIANTLAB.NS</t>
+          <t>YUKEN.NS</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>Valiant Laboratories Limited</t>
+          <t>Yuken India Limited</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr"/>
@@ -5094,111 +5094,111 @@
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP30" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.04229064593422944</v>
+        <v>0.0694281728976802</v>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS30" t="n">
         <v>86</v>
       </c>
       <c r="AT30" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1085.699951171875</v>
+        <v>417.8500061035156</v>
       </c>
       <c r="B31" t="n">
-        <v>1124.849975585938</v>
+        <v>469</v>
       </c>
       <c r="C31" t="n">
-        <v>1060.550048828125</v>
+        <v>414.5499877929688</v>
       </c>
       <c r="D31" t="n">
-        <v>1113.75</v>
+        <v>463.4500122070312</v>
       </c>
       <c r="E31" t="n">
-        <v>35432</v>
+        <v>10401534</v>
       </c>
       <c r="F31" t="n">
-        <v>1085.699951171875</v>
+        <v>417.4500122070312</v>
       </c>
       <c r="G31" t="n">
-        <v>2.583591239720384</v>
+        <v>11.01928342433169</v>
       </c>
       <c r="H31" t="n">
-        <v>969.1599914550782</v>
+        <v>376.9125015258789</v>
       </c>
       <c r="I31" t="n">
-        <v>839.0899963378906</v>
+        <v>381.5609997558594</v>
       </c>
       <c r="J31" t="n">
-        <v>773.2919989013672</v>
+        <v>385.7770001220703</v>
       </c>
       <c r="K31" t="n">
-        <v>775.4384997558594</v>
+        <v>368.4205001831054</v>
       </c>
       <c r="L31" t="n">
-        <v>1035.996071624864</v>
+        <v>406.932875731272</v>
       </c>
       <c r="M31" t="n">
-        <v>973.217043701645</v>
+        <v>389.1526744553819</v>
       </c>
       <c r="N31" t="n">
-        <v>876.4770778251901</v>
+        <v>382.3194672036209</v>
       </c>
       <c r="O31" t="n">
-        <v>75.3699587091405</v>
+        <v>91.94474483361198</v>
       </c>
       <c r="P31" t="n">
-        <v>51.38927786690848</v>
+        <v>20.04643249511719</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.614076576153399</v>
+        <v>4.325478901090652</v>
       </c>
       <c r="R31" t="n">
-        <v>29114.65</v>
+        <v>926456.55</v>
       </c>
       <c r="S31" t="n">
-        <v>1.216981828735705</v>
+        <v>11.22722269058382</v>
       </c>
       <c r="T31" t="n">
-        <v>1134.699951171875</v>
+        <v>469</v>
       </c>
       <c r="U31" t="n">
-        <v>584.0999755859375</v>
+        <v>242.25</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.846298763848424</v>
+        <v>-1.183366267157516</v>
       </c>
       <c r="W31" t="n">
-        <v>90.67797407160414</v>
+        <v>91.31063455398606</v>
       </c>
       <c r="X31" t="n">
-        <v>43.62841158269227</v>
+        <v>25.79376337003397</v>
       </c>
       <c r="Y31" t="b">
         <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>812</v>
+        <v>349.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1134.699951171875</v>
+        <v>444</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Strong Uptrend</t>
+          <t>Uptrend</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5208,22 +5208,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Near Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>YUKEN</t>
+          <t>SMSPHARMA</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>YUKEN.NS</t>
+          <t>SMSPHARMA.NS</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>Yuken India Limited</t>
+          <t>SMS Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr"/>
@@ -5240,144 +5240,144 @@
       </c>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>52W High Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP31" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.0694281728976802</v>
+        <v>-0.1703153251137194</v>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS31" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="AT31" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1948</v>
+        <v>1629.900024414062</v>
       </c>
       <c r="B32" t="n">
-        <v>2044.400024414062</v>
+        <v>1691.5</v>
       </c>
       <c r="C32" t="n">
-        <v>1909.400024414062</v>
+        <v>1600.099975585938</v>
       </c>
       <c r="D32" t="n">
-        <v>2020.099975585938</v>
+        <v>1674.699951171875</v>
       </c>
       <c r="E32" t="n">
-        <v>301736</v>
+        <v>352268</v>
       </c>
       <c r="F32" t="n">
-        <v>1949.099975585938</v>
+        <v>1640.300048828125</v>
       </c>
       <c r="G32" t="n">
-        <v>3.642706935987516</v>
+        <v>2.097171329618996</v>
       </c>
       <c r="H32" t="n">
-        <v>1667.385003662109</v>
+        <v>1648.340002441406</v>
       </c>
       <c r="I32" t="n">
-        <v>1684.426008300781</v>
+        <v>1554.631999511719</v>
       </c>
       <c r="J32" t="n">
-        <v>1568.246002197266</v>
+        <v>1364.323999023437</v>
       </c>
       <c r="K32" t="n">
-        <v>1348.079500427246</v>
+        <v>1176.877503356934</v>
       </c>
       <c r="L32" t="n">
-        <v>1822.388395938136</v>
+        <v>1648.996303763124</v>
       </c>
       <c r="M32" t="n">
-        <v>1727.065981002558</v>
+        <v>1634.26688743649</v>
       </c>
       <c r="N32" t="n">
-        <v>1656.209943212551</v>
+        <v>1544.718908589615</v>
       </c>
       <c r="O32" t="n">
-        <v>85.54993629647717</v>
+        <v>57.09648452653543</v>
       </c>
       <c r="P32" t="n">
-        <v>90.99286760602679</v>
+        <v>58.3857160295759</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.504374471844344</v>
+        <v>3.486338910365427</v>
       </c>
       <c r="R32" t="n">
-        <v>170549.1</v>
+        <v>232744</v>
       </c>
       <c r="S32" t="n">
-        <v>1.769203120978064</v>
+        <v>1.513542776612931</v>
       </c>
       <c r="T32" t="n">
-        <v>2044.400024414062</v>
+        <v>1717</v>
       </c>
       <c r="U32" t="n">
-        <v>890</v>
+        <v>726.4500122070312</v>
       </c>
       <c r="V32" t="n">
-        <v>-1.188615170120121</v>
+        <v>-2.463602144911182</v>
       </c>
       <c r="W32" t="n">
-        <v>126.9775253467345</v>
+        <v>130.5320287742801</v>
       </c>
       <c r="X32" t="n">
-        <v>49.85021098130402</v>
+        <v>42.30027733514738</v>
       </c>
       <c r="Y32" t="b">
         <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>1527.099975585938</v>
+        <v>1572.199951171875</v>
       </c>
       <c r="AA32" t="n">
-        <v>1998</v>
+        <v>1717</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Uptrend</t>
+          <t>Strong Uptrend</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>VENUSPIPES</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>VENUSPIPES.NS</t>
+          <t>AETHER.NS</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Venus Pipes &amp; Tubes Limited</t>
+          <t>Aether Industries Limited</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr"/>
@@ -5394,115 +5394,115 @@
       </c>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>52W High Watch</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP32" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-0.0448275366854716</v>
+        <v>0.4126834032012195</v>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS32" t="n">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="AT32" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1629.900024414062</v>
+        <v>970</v>
       </c>
       <c r="B33" t="n">
-        <v>1691.5</v>
+        <v>981.9000244140625</v>
       </c>
       <c r="C33" t="n">
-        <v>1600.099975585938</v>
+        <v>931</v>
       </c>
       <c r="D33" t="n">
-        <v>1674.699951171875</v>
+        <v>968.75</v>
       </c>
       <c r="E33" t="n">
-        <v>352268</v>
+        <v>204430</v>
       </c>
       <c r="F33" t="n">
-        <v>1640.300048828125</v>
+        <v>968.2000122070312</v>
       </c>
       <c r="G33" t="n">
-        <v>2.097171329618996</v>
+        <v>0.05680518343673668</v>
       </c>
       <c r="H33" t="n">
-        <v>1648.340002441406</v>
+        <v>900.2725006103516</v>
       </c>
       <c r="I33" t="n">
-        <v>1554.631999511719</v>
+        <v>894.4460021972657</v>
       </c>
       <c r="J33" t="n">
-        <v>1364.323999023437</v>
+        <v>863.7015008544922</v>
       </c>
       <c r="K33" t="n">
-        <v>1176.877503356934</v>
+        <v>789.9702496337891</v>
       </c>
       <c r="L33" t="n">
-        <v>1648.996303763124</v>
+        <v>933.6553974845219</v>
       </c>
       <c r="M33" t="n">
-        <v>1634.26688743649</v>
+        <v>912.2938894255869</v>
       </c>
       <c r="N33" t="n">
-        <v>1544.718908589615</v>
+        <v>887.7362467497567</v>
       </c>
       <c r="O33" t="n">
-        <v>57.09648452653543</v>
+        <v>66.54121283173092</v>
       </c>
       <c r="P33" t="n">
-        <v>58.3857160295759</v>
+        <v>43.96429007393973</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.486338910365427</v>
+        <v>4.538249297955069</v>
       </c>
       <c r="R33" t="n">
-        <v>232744</v>
+        <v>138541.4</v>
       </c>
       <c r="S33" t="n">
-        <v>1.513542776612931</v>
+        <v>1.475587802635169</v>
       </c>
       <c r="T33" t="n">
-        <v>1717</v>
+        <v>992.5999755859375</v>
       </c>
       <c r="U33" t="n">
-        <v>726.4500122070312</v>
+        <v>574</v>
       </c>
       <c r="V33" t="n">
-        <v>-2.463602144911182</v>
+        <v>-2.402778175755921</v>
       </c>
       <c r="W33" t="n">
-        <v>130.5320287742801</v>
+        <v>68.77177700348433</v>
       </c>
       <c r="X33" t="n">
-        <v>42.30027733514738</v>
+        <v>22.63120040901399</v>
       </c>
       <c r="Y33" t="b">
         <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>1572.199951171875</v>
+        <v>816</v>
       </c>
       <c r="AA33" t="n">
-        <v>1717</v>
+        <v>992.5999755859375</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5521,17 +5521,17 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>AETHER.NS</t>
+          <t>KSL.NS</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>Aether Industries Limited</t>
+          <t>Kalyani Steels Limited</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr"/>
@@ -5556,107 +5556,107 @@
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP33" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.4126834032012195</v>
+        <v>0.1561373197115385</v>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>Strong price trend | Positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS33" t="n">
         <v>104</v>
       </c>
       <c r="AT33" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>970</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="B34" t="n">
-        <v>981.9000244140625</v>
+        <v>84.59999847412109</v>
       </c>
       <c r="C34" t="n">
-        <v>931</v>
+        <v>81.19999694824219</v>
       </c>
       <c r="D34" t="n">
-        <v>968.75</v>
+        <v>84.23000335693359</v>
       </c>
       <c r="E34" t="n">
-        <v>204430</v>
+        <v>16781160</v>
       </c>
       <c r="F34" t="n">
-        <v>968.2000122070312</v>
+        <v>83.05000305175781</v>
       </c>
       <c r="G34" t="n">
-        <v>0.05680518343673668</v>
+        <v>1.420831140054735</v>
       </c>
       <c r="H34" t="n">
-        <v>900.2725006103516</v>
+        <v>71.80400009155274</v>
       </c>
       <c r="I34" t="n">
-        <v>894.4460021972657</v>
+        <v>71.35100006103515</v>
       </c>
       <c r="J34" t="n">
-        <v>863.7015008544922</v>
+        <v>62.73239978790284</v>
       </c>
       <c r="K34" t="n">
-        <v>789.9702496337891</v>
+        <v>49.33869986534118</v>
       </c>
       <c r="L34" t="n">
-        <v>933.6553974845219</v>
+        <v>77.5775697266003</v>
       </c>
       <c r="M34" t="n">
-        <v>912.2938894255869</v>
+        <v>73.89255627812966</v>
       </c>
       <c r="N34" t="n">
-        <v>887.7362467497567</v>
+        <v>69.74176446820893</v>
       </c>
       <c r="O34" t="n">
-        <v>66.54121283173092</v>
+        <v>80.66525731818581</v>
       </c>
       <c r="P34" t="n">
-        <v>43.96429007393973</v>
+        <v>2.95357186453683</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.538249297955069</v>
+        <v>3.50655555838073</v>
       </c>
       <c r="R34" t="n">
-        <v>138541.4</v>
+        <v>12873213.45</v>
       </c>
       <c r="S34" t="n">
-        <v>1.475587802635169</v>
+        <v>1.303571953124105</v>
       </c>
       <c r="T34" t="n">
-        <v>992.5999755859375</v>
+        <v>84.59999847412109</v>
       </c>
       <c r="U34" t="n">
-        <v>574</v>
+        <v>30</v>
       </c>
       <c r="V34" t="n">
-        <v>-2.402778175755921</v>
+        <v>-0.4373464821050564</v>
       </c>
       <c r="W34" t="n">
-        <v>68.77177700348433</v>
+        <v>180.7666778564453</v>
       </c>
       <c r="X34" t="n">
-        <v>22.63120040901399</v>
+        <v>70.71792241550816</v>
       </c>
       <c r="Y34" t="b">
         <v>1</v>
       </c>
       <c r="Z34" t="n">
-        <v>816</v>
+        <v>65</v>
       </c>
       <c r="AA34" t="n">
-        <v>992.5999755859375</v>
+        <v>83.5</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -5670,22 +5670,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Breakout - Volume Confirmation Required</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>KSL.NS</t>
+          <t>PAISALO.NS</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Kalyani Steels Limited</t>
+          <t>Paisalo Digital Limited</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr"/>
@@ -5710,107 +5710,107 @@
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP34" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.1561373197115385</v>
+        <v>-0.03796168640139019</v>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS34" t="n">
         <v>104</v>
       </c>
       <c r="AT34" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>81.72000122070312</v>
+        <v>870</v>
       </c>
       <c r="B35" t="n">
+        <v>897.4500122070312</v>
+      </c>
+      <c r="C35" t="n">
+        <v>830</v>
+      </c>
+      <c r="D35" t="n">
+        <v>897.4000244140625</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2409510</v>
+      </c>
+      <c r="F35" t="n">
+        <v>854.75</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.989765944903479</v>
+      </c>
+      <c r="H35" t="n">
+        <v>711.977505493164</v>
+      </c>
+      <c r="I35" t="n">
+        <v>625.8870037841797</v>
+      </c>
+      <c r="J35" t="n">
+        <v>559.2561999511719</v>
+      </c>
+      <c r="K35" t="n">
+        <v>352.3013998413086</v>
+      </c>
+      <c r="L35" t="n">
+        <v>800.2501003209892</v>
+      </c>
+      <c r="M35" t="n">
+        <v>735.3393947675986</v>
+      </c>
+      <c r="N35" t="n">
+        <v>652.051658456534</v>
+      </c>
+      <c r="O35" t="n">
+        <v>85.69541211744804</v>
+      </c>
+      <c r="P35" t="n">
+        <v>45.09286063058035</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.024833898352381</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1650444.1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.459916152264715</v>
+      </c>
+      <c r="T35" t="n">
+        <v>897.4500122070312</v>
+      </c>
+      <c r="U35" t="n">
         <v>84.59999847412109</v>
       </c>
-      <c r="C35" t="n">
-        <v>81.19999694824219</v>
-      </c>
-      <c r="D35" t="n">
-        <v>84.23000335693359</v>
-      </c>
-      <c r="E35" t="n">
-        <v>16781160</v>
-      </c>
-      <c r="F35" t="n">
-        <v>83.05000305175781</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.420831140054735</v>
-      </c>
-      <c r="H35" t="n">
-        <v>71.80400009155274</v>
-      </c>
-      <c r="I35" t="n">
-        <v>71.35100006103515</v>
-      </c>
-      <c r="J35" t="n">
-        <v>62.73239978790284</v>
-      </c>
-      <c r="K35" t="n">
-        <v>49.33869986534118</v>
-      </c>
-      <c r="L35" t="n">
-        <v>77.5775697266003</v>
-      </c>
-      <c r="M35" t="n">
-        <v>73.89255627812966</v>
-      </c>
-      <c r="N35" t="n">
-        <v>69.74176446820893</v>
-      </c>
-      <c r="O35" t="n">
-        <v>80.66525731818581</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.95357186453683</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.50655555838073</v>
-      </c>
-      <c r="R35" t="n">
-        <v>12873213.45</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.303571953124105</v>
-      </c>
-      <c r="T35" t="n">
-        <v>84.59999847412109</v>
-      </c>
-      <c r="U35" t="n">
-        <v>30</v>
-      </c>
       <c r="V35" t="n">
-        <v>-0.4373464821050564</v>
+        <v>-0.005569980755342437</v>
       </c>
       <c r="W35" t="n">
-        <v>180.7666778564453</v>
+        <v>960.7565491724857</v>
       </c>
       <c r="X35" t="n">
-        <v>70.71792241550816</v>
+        <v>154.7250805186381</v>
       </c>
       <c r="Y35" t="b">
         <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>65</v>
+        <v>601</v>
       </c>
       <c r="AA35" t="n">
-        <v>83.5</v>
+        <v>897.2999877929688</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
@@ -5829,17 +5829,17 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>PAISALO.NS</t>
+          <t>STLTECH.NS</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>Paisalo Digital Limited</t>
+          <t>Sterlite Technologies Limited</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr"/>
@@ -5864,13 +5864,13 @@
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP35" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AQ35" t="n">
-        <v>-0.03796168640139019</v>
+        <v>-0.0003375054414772977</v>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
@@ -5881,90 +5881,90 @@
         <v>104</v>
       </c>
       <c r="AT35" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>870</v>
+        <v>1560.900024414062</v>
       </c>
       <c r="B36" t="n">
-        <v>897.4500122070312</v>
+        <v>1614.900024414062</v>
       </c>
       <c r="C36" t="n">
-        <v>830</v>
+        <v>1531</v>
       </c>
       <c r="D36" t="n">
-        <v>897.4000244140625</v>
+        <v>1610</v>
       </c>
       <c r="E36" t="n">
-        <v>2409510</v>
+        <v>296742</v>
       </c>
       <c r="F36" t="n">
-        <v>854.75</v>
+        <v>1568.099975585938</v>
       </c>
       <c r="G36" t="n">
-        <v>4.989765944903479</v>
+        <v>2.672025066412376</v>
       </c>
       <c r="H36" t="n">
-        <v>711.977505493164</v>
+        <v>1513.160003662109</v>
       </c>
       <c r="I36" t="n">
-        <v>625.8870037841797</v>
+        <v>1370.658005371094</v>
       </c>
       <c r="J36" t="n">
-        <v>559.2561999511719</v>
+        <v>1211.910009155273</v>
       </c>
       <c r="K36" t="n">
-        <v>352.3013998413086</v>
+        <v>1052.19325378418</v>
       </c>
       <c r="L36" t="n">
-        <v>800.2501003209892</v>
+        <v>1550.656017017739</v>
       </c>
       <c r="M36" t="n">
-        <v>735.3393947675986</v>
+        <v>1503.861284876644</v>
       </c>
       <c r="N36" t="n">
-        <v>652.051658456534</v>
+        <v>1389.632570402933</v>
       </c>
       <c r="O36" t="n">
-        <v>85.69541211744804</v>
+        <v>62.81873341658114</v>
       </c>
       <c r="P36" t="n">
-        <v>45.09286063058035</v>
+        <v>65.84286934988839</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.024833898352381</v>
+        <v>4.089619214278782</v>
       </c>
       <c r="R36" t="n">
-        <v>1650444.1</v>
+        <v>224684.6</v>
       </c>
       <c r="S36" t="n">
-        <v>1.459916152264715</v>
+        <v>1.320704667787646</v>
       </c>
       <c r="T36" t="n">
-        <v>897.4500122070312</v>
+        <v>1652.800048828125</v>
       </c>
       <c r="U36" t="n">
-        <v>84.59999847412109</v>
+        <v>695</v>
       </c>
       <c r="V36" t="n">
-        <v>-0.005569980755342437</v>
+        <v>-2.589547892285656</v>
       </c>
       <c r="W36" t="n">
-        <v>960.7565491724857</v>
+        <v>131.6546762589928</v>
       </c>
       <c r="X36" t="n">
-        <v>154.7250805186381</v>
+        <v>53.01371627404814</v>
       </c>
       <c r="Y36" t="b">
         <v>1</v>
       </c>
       <c r="Z36" t="n">
-        <v>601</v>
+        <v>1421.199951171875</v>
       </c>
       <c r="AA36" t="n">
-        <v>897.2999877929688</v>
+        <v>1652.800048828125</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Breakout - Volume Confirmation Required</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>STLTECH.NS</t>
+          <t>UNIMECH.NS</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Sterlite Technologies Limited</t>
+          <t>Unimech Aerospace and Manufacturing Limited</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr"/>
@@ -6018,107 +6018,107 @@
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP36" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AQ36" t="n">
-        <v>-0.0003375054414772977</v>
+        <v>0.2266951152490867</v>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS36" t="n">
         <v>104</v>
       </c>
       <c r="AT36" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1560.900024414062</v>
+        <v>877.4000244140625</v>
       </c>
       <c r="B37" t="n">
-        <v>1614.900024414062</v>
+        <v>889.8499755859375</v>
       </c>
       <c r="C37" t="n">
-        <v>1531</v>
+        <v>866</v>
       </c>
       <c r="D37" t="n">
-        <v>1610</v>
+        <v>872</v>
       </c>
       <c r="E37" t="n">
-        <v>296742</v>
+        <v>482620</v>
       </c>
       <c r="F37" t="n">
-        <v>1568.099975585938</v>
+        <v>884.4000244140625</v>
       </c>
       <c r="G37" t="n">
-        <v>2.672025066412376</v>
+        <v>-1.402083228375961</v>
       </c>
       <c r="H37" t="n">
-        <v>1513.160003662109</v>
+        <v>837.6825103759766</v>
       </c>
       <c r="I37" t="n">
-        <v>1370.658005371094</v>
+        <v>750.6360070800781</v>
       </c>
       <c r="J37" t="n">
-        <v>1211.910009155273</v>
+        <v>663.5100042724609</v>
       </c>
       <c r="K37" t="n">
-        <v>1052.19325378418</v>
+        <v>613.9637522888183</v>
       </c>
       <c r="L37" t="n">
-        <v>1550.656017017739</v>
+        <v>851.5186630220543</v>
       </c>
       <c r="M37" t="n">
-        <v>1503.861284876644</v>
+        <v>829.3507536840106</v>
       </c>
       <c r="N37" t="n">
-        <v>1389.632570402933</v>
+        <v>765.0175172642181</v>
       </c>
       <c r="O37" t="n">
-        <v>62.81873341658114</v>
+        <v>61.78474734533123</v>
       </c>
       <c r="P37" t="n">
-        <v>65.84286934988839</v>
+        <v>37.89644077845982</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.089619214278782</v>
+        <v>4.345922107621539</v>
       </c>
       <c r="R37" t="n">
-        <v>224684.6</v>
+        <v>392861.65</v>
       </c>
       <c r="S37" t="n">
-        <v>1.320704667787646</v>
+        <v>1.22847317878953</v>
       </c>
       <c r="T37" t="n">
-        <v>1652.800048828125</v>
+        <v>896</v>
       </c>
       <c r="U37" t="n">
-        <v>695</v>
+        <v>462</v>
       </c>
       <c r="V37" t="n">
-        <v>-2.589547892285656</v>
+        <v>-2.678571428571428</v>
       </c>
       <c r="W37" t="n">
-        <v>131.6546762589928</v>
+        <v>88.74458874458875</v>
       </c>
       <c r="X37" t="n">
-        <v>53.01371627404814</v>
+        <v>42.02792864387168</v>
       </c>
       <c r="Y37" t="b">
         <v>1</v>
       </c>
       <c r="Z37" t="n">
-        <v>1421.199951171875</v>
+        <v>795.5999755859375</v>
       </c>
       <c r="AA37" t="n">
-        <v>1652.800048828125</v>
+        <v>896</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
@@ -6137,17 +6137,17 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>UNIMECH.NS</t>
+          <t>VARROC.NS</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Unimech Aerospace and Manufacturing Limited</t>
+          <t>Varroc Engineering Limited</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr"/>
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP37" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.2266951152490867</v>
+        <v>0.314136025270464</v>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
@@ -6189,94 +6189,94 @@
         <v>104</v>
       </c>
       <c r="AT37" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>877.4000244140625</v>
+        <v>1948</v>
       </c>
       <c r="B38" t="n">
-        <v>889.8499755859375</v>
+        <v>2044.400024414062</v>
       </c>
       <c r="C38" t="n">
-        <v>866</v>
+        <v>1909.400024414062</v>
       </c>
       <c r="D38" t="n">
-        <v>872</v>
+        <v>2020.099975585938</v>
       </c>
       <c r="E38" t="n">
-        <v>482620</v>
+        <v>301736</v>
       </c>
       <c r="F38" t="n">
-        <v>884.4000244140625</v>
+        <v>1949.099975585938</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.402083228375961</v>
+        <v>3.642706935987516</v>
       </c>
       <c r="H38" t="n">
-        <v>837.6825103759766</v>
+        <v>1667.385003662109</v>
       </c>
       <c r="I38" t="n">
-        <v>750.6360070800781</v>
+        <v>1684.426008300781</v>
       </c>
       <c r="J38" t="n">
-        <v>663.5100042724609</v>
+        <v>1568.246002197266</v>
       </c>
       <c r="K38" t="n">
-        <v>613.9637522888183</v>
+        <v>1348.079500427246</v>
       </c>
       <c r="L38" t="n">
-        <v>851.5186630220543</v>
+        <v>1822.388395938136</v>
       </c>
       <c r="M38" t="n">
-        <v>829.3507536840106</v>
+        <v>1727.065981002558</v>
       </c>
       <c r="N38" t="n">
-        <v>765.0175172642181</v>
+        <v>1656.209943212551</v>
       </c>
       <c r="O38" t="n">
-        <v>61.78474734533123</v>
+        <v>85.54993629647717</v>
       </c>
       <c r="P38" t="n">
-        <v>37.89644077845982</v>
+        <v>90.99286760602679</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.345922107621539</v>
+        <v>4.504374471844344</v>
       </c>
       <c r="R38" t="n">
-        <v>392861.65</v>
+        <v>170549.1</v>
       </c>
       <c r="S38" t="n">
-        <v>1.22847317878953</v>
+        <v>1.769203120978064</v>
       </c>
       <c r="T38" t="n">
-        <v>896</v>
+        <v>2044.400024414062</v>
       </c>
       <c r="U38" t="n">
-        <v>462</v>
+        <v>890</v>
       </c>
       <c r="V38" t="n">
-        <v>-2.678571428571428</v>
+        <v>-1.188615170120121</v>
       </c>
       <c r="W38" t="n">
-        <v>88.74458874458875</v>
+        <v>126.9775253467345</v>
       </c>
       <c r="X38" t="n">
-        <v>42.02792864387168</v>
+        <v>49.85021098130402</v>
       </c>
       <c r="Y38" t="b">
         <v>1</v>
       </c>
       <c r="Z38" t="n">
-        <v>795.5999755859375</v>
+        <v>1527.099975585938</v>
       </c>
       <c r="AA38" t="n">
-        <v>896</v>
+        <v>1998</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Strong Uptrend</t>
+          <t>Uptrend</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6286,22 +6286,22 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>VENUSPIPES</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>VARROC.NS</t>
+          <t>VENUSPIPES.NS</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Varroc Engineering Limited</t>
+          <t>Venus Pipes &amp; Tubes Limited</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr"/>
@@ -6318,113 +6318,115 @@
       </c>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>52W High Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP38" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.314136025270464</v>
+        <v>-0.0448275366854716</v>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS38" t="n">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="AT38" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5.179999828338623</v>
+        <v>95.70999908447266</v>
       </c>
       <c r="B39" t="n">
-        <v>5.179999828338623</v>
+        <v>100.3000030517578</v>
       </c>
       <c r="C39" t="n">
-        <v>5.179999828338623</v>
+        <v>94.91999816894531</v>
       </c>
       <c r="D39" t="n">
-        <v>5.179999828338623</v>
+        <v>98.88999938964844</v>
       </c>
       <c r="E39" t="n">
-        <v>85364</v>
+        <v>369808</v>
       </c>
       <c r="F39" t="n">
-        <v>5.079999923706055</v>
+        <v>95.70999908447266</v>
       </c>
       <c r="G39" t="n">
-        <v>1.96850208926016</v>
+        <v>3.322537180644147</v>
       </c>
       <c r="H39" t="n">
-        <v>4.302999973297119</v>
+        <v>88.04000015258789</v>
       </c>
       <c r="I39" t="n">
-        <v>3.263600006103516</v>
+        <v>83.63339996337891</v>
       </c>
       <c r="J39" t="n">
-        <v>2.656600006818771</v>
+        <v>84.46020004272461</v>
       </c>
       <c r="K39" t="n">
-        <v>2.188500003218651</v>
+        <v>77.17160009384155</v>
       </c>
       <c r="L39" t="n">
-        <v>4.787722044403476</v>
+        <v>94.74560625133056</v>
       </c>
       <c r="M39" t="n">
-        <v>4.340786985476073</v>
+        <v>90.27135373959797</v>
       </c>
       <c r="N39" t="n">
-        <v>3.568518653055021</v>
-      </c>
-      <c r="O39" t="inlineStr"/>
+        <v>85.86508488006056</v>
+      </c>
+      <c r="O39" t="n">
+        <v>73.30698796304598</v>
+      </c>
       <c r="P39" t="n">
-        <v>0.09642853055681501</v>
+        <v>4.388572147914341</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.861554705644507</v>
+        <v>4.437832111437677</v>
       </c>
       <c r="R39" t="n">
-        <v>32985.95</v>
+        <v>234225.8</v>
       </c>
       <c r="S39" t="n">
-        <v>2.587889692429656</v>
+        <v>1.578852543144265</v>
       </c>
       <c r="T39" t="n">
-        <v>5.179999828338623</v>
+        <v>101.2900009155273</v>
       </c>
       <c r="U39" t="n">
-        <v>1.299999952316284</v>
+        <v>50.31000137329102</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>-2.369435782590654</v>
       </c>
       <c r="W39" t="n">
-        <v>298.4615398722993</v>
+        <v>96.56131323850046</v>
       </c>
       <c r="X39" t="n">
-        <v>136.6917898432872</v>
+        <v>28.14299466305878</v>
       </c>
       <c r="Y39" t="b">
         <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.5</v>
+        <v>74.59999847412109</v>
       </c>
       <c r="AA39" t="n">
-        <v>5.079999923706055</v>
+        <v>101.2900009155273</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -6433,27 +6435,27 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Insufficient Data</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>IMPEXFERRO</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>IMPEXFERRO.NS</t>
+          <t>AAREYDRUGS.NS</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Impex Ferro Tech Limited</t>
+          <t>Aarey Drugs &amp; Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr"/>
@@ -6470,113 +6472,115 @@
       </c>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>52W High Watch</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP39" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ39" t="n">
-        <v>-0.05952375883958259</v>
+        <v>0.09880615213747107</v>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>Strong price trend | Confirmed price breakout | Volume is more than 2x average | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS39" t="n">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="AT39" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3.329999923706055</v>
+        <v>1943</v>
       </c>
       <c r="B40" t="n">
-        <v>3.329999923706055</v>
+        <v>1981.800048828125</v>
       </c>
       <c r="C40" t="n">
-        <v>3.319999933242798</v>
+        <v>1918.099975585938</v>
       </c>
       <c r="D40" t="n">
-        <v>3.329999923706055</v>
+        <v>1969</v>
       </c>
       <c r="E40" t="n">
-        <v>2178546</v>
+        <v>2277375</v>
       </c>
       <c r="F40" t="n">
-        <v>3.269999980926514</v>
+        <v>1945</v>
       </c>
       <c r="G40" t="n">
-        <v>1.834860646162473</v>
+        <v>1.233933161953726</v>
       </c>
       <c r="H40" t="n">
-        <v>2.779500007629395</v>
+        <v>1870.445001220703</v>
       </c>
       <c r="I40" t="n">
-        <v>2.266599998474121</v>
+        <v>1751.362004394531</v>
       </c>
       <c r="J40" t="n">
-        <v>1.686199998855591</v>
+        <v>1544.505504150391</v>
       </c>
       <c r="K40" t="n">
-        <v>1.422499998807907</v>
+        <v>1291.111001586914</v>
       </c>
       <c r="L40" t="n">
-        <v>3.085268005688187</v>
+        <v>1916.655556912799</v>
       </c>
       <c r="M40" t="n">
-        <v>2.832618148765642</v>
+        <v>1876.917313685952</v>
       </c>
       <c r="N40" t="n">
-        <v>2.36228866312997</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>1757.411853934276</v>
+      </c>
+      <c r="O40" t="n">
+        <v>70.89589078925341</v>
+      </c>
       <c r="P40" t="n">
-        <v>0.06071427890232631</v>
+        <v>53.50715855189732</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.823251660461169</v>
+        <v>2.717478849766243</v>
       </c>
       <c r="R40" t="n">
-        <v>475284.4</v>
+        <v>3578275.7</v>
       </c>
       <c r="S40" t="n">
-        <v>4.583668220543321</v>
+        <v>0.6364448105549831</v>
       </c>
       <c r="T40" t="n">
-        <v>3.329999923706055</v>
+        <v>1981.800048828125</v>
       </c>
       <c r="U40" t="n">
-        <v>0.6800000071525574</v>
+        <v>823.0999755859375</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>-0.6458799330282541</v>
       </c>
       <c r="W40" t="n">
-        <v>389.7058659822885</v>
+        <v>139.2175991255903</v>
       </c>
       <c r="X40" t="n">
-        <v>134.0948981719988</v>
+        <v>52.5043158628412</v>
       </c>
       <c r="Y40" t="b">
         <v>1</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.319999933242798</v>
+        <v>1769.400024414062</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.269999980926514</v>
+        <v>1955</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
@@ -6585,27 +6589,27 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Insufficient Data</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>Breakout - Volume Confirmation Required</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>SUPREMEENG</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>SUPREMEENG.NS</t>
+          <t>LAURUSLABS.NS</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Supreme Engineering Limited</t>
+          <t>Laurus Labs Limited</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr"/>
@@ -6622,115 +6626,115 @@
       </c>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>52W High Watch</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP40" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ40" t="n">
-        <v>-0.05940588450106899</v>
+        <v>-0.07014028914032767</v>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>Strong price trend | Confirmed price breakout | Volume is more than 2x average | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS40" t="n">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="AT40" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>95.70999908447266</v>
+        <v>1432</v>
       </c>
       <c r="B41" t="n">
-        <v>100.3000030517578</v>
+        <v>1442</v>
       </c>
       <c r="C41" t="n">
-        <v>94.91999816894531</v>
+        <v>1401.099975585938</v>
       </c>
       <c r="D41" t="n">
-        <v>98.88999938964844</v>
+        <v>1435.699951171875</v>
       </c>
       <c r="E41" t="n">
-        <v>369808</v>
+        <v>107494</v>
       </c>
       <c r="F41" t="n">
-        <v>95.70999908447266</v>
+        <v>1432</v>
       </c>
       <c r="G41" t="n">
-        <v>3.322537180644147</v>
+        <v>0.2583764784828801</v>
       </c>
       <c r="H41" t="n">
-        <v>88.04000015258789</v>
+        <v>1399.414996337891</v>
       </c>
       <c r="I41" t="n">
-        <v>83.63339996337891</v>
+        <v>1352.27599609375</v>
       </c>
       <c r="J41" t="n">
-        <v>84.46020004272461</v>
+        <v>1326.073996582031</v>
       </c>
       <c r="K41" t="n">
-        <v>77.17160009384155</v>
+        <v>1236.42</v>
       </c>
       <c r="L41" t="n">
-        <v>94.74560625133056</v>
+        <v>1413.6383949649</v>
       </c>
       <c r="M41" t="n">
-        <v>90.27135373959797</v>
+        <v>1395.617073818971</v>
       </c>
       <c r="N41" t="n">
-        <v>85.86508488006056</v>
+        <v>1362.66152509005</v>
       </c>
       <c r="O41" t="n">
-        <v>73.30698796304598</v>
+        <v>62.8078822671039</v>
       </c>
       <c r="P41" t="n">
-        <v>4.388572147914341</v>
+        <v>33.82856968470982</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.437832111437677</v>
+        <v>2.356242309341698</v>
       </c>
       <c r="R41" t="n">
-        <v>234225.8</v>
+        <v>172230.6</v>
       </c>
       <c r="S41" t="n">
-        <v>1.578852543144265</v>
+        <v>0.6241283488532235</v>
       </c>
       <c r="T41" t="n">
-        <v>101.2900009155273</v>
+        <v>1479.599975585938</v>
       </c>
       <c r="U41" t="n">
-        <v>50.31000137329102</v>
+        <v>1007.099975585938</v>
       </c>
       <c r="V41" t="n">
-        <v>-2.369435782590654</v>
+        <v>-2.967019812005446</v>
       </c>
       <c r="W41" t="n">
-        <v>96.56131323850046</v>
+        <v>42.55783794817145</v>
       </c>
       <c r="X41" t="n">
-        <v>28.14299466305878</v>
+        <v>16.11749657655772</v>
       </c>
       <c r="Y41" t="b">
         <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>74.59999847412109</v>
+        <v>1342.800048828125</v>
       </c>
       <c r="AA41" t="n">
-        <v>101.2900009155273</v>
+        <v>1452.699951171875</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
@@ -6749,17 +6753,17 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>KPIL</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>AAREYDRUGS.NS</t>
+          <t>KPIL.NS</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>Aarey Drugs &amp; Pharmaceuticals Limited</t>
+          <t>Kalpataru Projects International Limited</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr"/>
@@ -6776,7 +6780,7 @@
       </c>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
@@ -6784,107 +6788,107 @@
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP41" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.09880615213747107</v>
+        <v>0.1829926573775748</v>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS41" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="AT41" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1943</v>
+        <v>22385</v>
       </c>
       <c r="B42" t="n">
-        <v>1981.800048828125</v>
+        <v>24050</v>
       </c>
       <c r="C42" t="n">
-        <v>1918.099975585938</v>
+        <v>22055</v>
       </c>
       <c r="D42" t="n">
-        <v>1969</v>
+        <v>23630</v>
       </c>
       <c r="E42" t="n">
-        <v>2277375</v>
+        <v>65881</v>
       </c>
       <c r="F42" t="n">
-        <v>1945</v>
+        <v>22385</v>
       </c>
       <c r="G42" t="n">
-        <v>1.233933161953726</v>
+        <v>5.561760107214653</v>
       </c>
       <c r="H42" t="n">
-        <v>1870.445001220703</v>
+        <v>21667.5</v>
       </c>
       <c r="I42" t="n">
-        <v>1751.362004394531</v>
+        <v>19458.84</v>
       </c>
       <c r="J42" t="n">
-        <v>1544.505504150391</v>
+        <v>18330.27</v>
       </c>
       <c r="K42" t="n">
-        <v>1291.111001586914</v>
+        <v>17928.25</v>
       </c>
       <c r="L42" t="n">
-        <v>1916.655556912799</v>
+        <v>22841.4052959534</v>
       </c>
       <c r="M42" t="n">
-        <v>1876.917313685952</v>
+        <v>21831.40202240128</v>
       </c>
       <c r="N42" t="n">
-        <v>1757.411853934276</v>
+        <v>20148.83613138522</v>
       </c>
       <c r="O42" t="n">
-        <v>70.89589078925341</v>
+        <v>68.59125263288317</v>
       </c>
       <c r="P42" t="n">
-        <v>53.50715855189732</v>
+        <v>1041.071428571429</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.717478849766243</v>
+        <v>4.405719122181247</v>
       </c>
       <c r="R42" t="n">
-        <v>3578275.7</v>
+        <v>58518.3</v>
       </c>
       <c r="S42" t="n">
-        <v>0.6364448105549831</v>
+        <v>1.125818760968791</v>
       </c>
       <c r="T42" t="n">
-        <v>1981.800048828125</v>
+        <v>24125</v>
       </c>
       <c r="U42" t="n">
-        <v>823.0999755859375</v>
+        <v>13498</v>
       </c>
       <c r="V42" t="n">
-        <v>-0.6458799330282541</v>
+        <v>-2.051813471502591</v>
       </c>
       <c r="W42" t="n">
-        <v>139.2175991255903</v>
+        <v>75.06297229219143</v>
       </c>
       <c r="X42" t="n">
-        <v>52.5043158628412</v>
+        <v>31.80315981760629</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>1769.400024414062</v>
+        <v>18871</v>
       </c>
       <c r="AA42" t="n">
-        <v>1955</v>
+        <v>24125</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
@@ -6898,22 +6902,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Breakout - Volume Confirmation Required</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>LAURUSLABS.NS</t>
+          <t>PTCIL.NS</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>Laurus Labs Limited</t>
+          <t>PTC Industries Limited</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr"/>
@@ -6930,7 +6934,7 @@
       </c>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
@@ -6938,107 +6942,107 @@
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP42" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AQ42" t="n">
-        <v>-0.07014028914032767</v>
+        <v>0.1040134482034041</v>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS42" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="AT42" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1432</v>
+        <v>408</v>
       </c>
       <c r="B43" t="n">
-        <v>1442</v>
+        <v>416.5</v>
       </c>
       <c r="C43" t="n">
-        <v>1401.099975585938</v>
+        <v>406</v>
       </c>
       <c r="D43" t="n">
-        <v>1435.699951171875</v>
+        <v>412.5499877929688</v>
       </c>
       <c r="E43" t="n">
-        <v>107494</v>
+        <v>3209425</v>
       </c>
       <c r="F43" t="n">
-        <v>1432</v>
+        <v>410.7999877929688</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2583764784828801</v>
+        <v>0.425998065238975</v>
       </c>
       <c r="H43" t="n">
-        <v>1399.414996337891</v>
+        <v>393.4124984741211</v>
       </c>
       <c r="I43" t="n">
-        <v>1352.27599609375</v>
+        <v>381.5749987792969</v>
       </c>
       <c r="J43" t="n">
-        <v>1326.073996582031</v>
+        <v>364.7274996948242</v>
       </c>
       <c r="K43" t="n">
-        <v>1236.42</v>
+        <v>336.3727499389648</v>
       </c>
       <c r="L43" t="n">
-        <v>1413.6383949649</v>
+        <v>405.8323899746489</v>
       </c>
       <c r="M43" t="n">
-        <v>1395.617073818971</v>
+        <v>396.9724348712864</v>
       </c>
       <c r="N43" t="n">
-        <v>1362.66152509005</v>
+        <v>383.5323839307324</v>
       </c>
       <c r="O43" t="n">
-        <v>62.8078822671039</v>
+        <v>65.29366249181774</v>
       </c>
       <c r="P43" t="n">
-        <v>33.82856968470982</v>
+        <v>8.960715157645089</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.356242309341698</v>
+        <v>2.172031371418164</v>
       </c>
       <c r="R43" t="n">
-        <v>172230.6</v>
+        <v>3376517.2</v>
       </c>
       <c r="S43" t="n">
-        <v>0.6241283488532235</v>
+        <v>0.950513446222042</v>
       </c>
       <c r="T43" t="n">
-        <v>1479.599975585938</v>
+        <v>420.3999938964844</v>
       </c>
       <c r="U43" t="n">
-        <v>1007.099975585938</v>
+        <v>261.6000061035156</v>
       </c>
       <c r="V43" t="n">
-        <v>-2.967019812005446</v>
+        <v>-1.867270746309416</v>
       </c>
       <c r="W43" t="n">
-        <v>42.55783794817145</v>
+        <v>57.70259104264773</v>
       </c>
       <c r="X43" t="n">
-        <v>16.11749657655772</v>
+        <v>22.64667333124528</v>
       </c>
       <c r="Y43" t="b">
         <v>1</v>
       </c>
       <c r="Z43" t="n">
-        <v>1342.800048828125</v>
+        <v>375</v>
       </c>
       <c r="AA43" t="n">
-        <v>1452.699951171875</v>
+        <v>420.3999938964844</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
@@ -7057,17 +7061,17 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>KPIL</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>KPIL.NS</t>
+          <t>RBLBANK.NS</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Kalpataru Projects International Limited</t>
+          <t>RBL Bank Limited</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr"/>
@@ -7092,13 +7096,13 @@
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP43" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.1829926573775748</v>
+        <v>0.2090548243796112</v>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
@@ -7109,90 +7113,90 @@
         <v>143</v>
       </c>
       <c r="AT43" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>22385</v>
+        <v>395.8500061035156</v>
       </c>
       <c r="B44" t="n">
-        <v>24050</v>
+        <v>396.8500061035156</v>
       </c>
       <c r="C44" t="n">
-        <v>22055</v>
+        <v>384.2000122070312</v>
       </c>
       <c r="D44" t="n">
-        <v>23630</v>
+        <v>393.7000122070312</v>
       </c>
       <c r="E44" t="n">
-        <v>65881</v>
+        <v>7473984</v>
       </c>
       <c r="F44" t="n">
-        <v>22385</v>
+        <v>392</v>
       </c>
       <c r="G44" t="n">
-        <v>5.561760107214653</v>
+        <v>0.4336765834263456</v>
       </c>
       <c r="H44" t="n">
-        <v>21667.5</v>
+        <v>360.9474990844727</v>
       </c>
       <c r="I44" t="n">
-        <v>19458.84</v>
+        <v>325.4839990234375</v>
       </c>
       <c r="J44" t="n">
-        <v>18330.27</v>
+        <v>282.1428994750976</v>
       </c>
       <c r="K44" t="n">
-        <v>17928.25</v>
+        <v>267.9290991210938</v>
       </c>
       <c r="L44" t="n">
-        <v>22841.4052959534</v>
+        <v>377.4684592602789</v>
       </c>
       <c r="M44" t="n">
-        <v>21831.40202240128</v>
+        <v>363.4923475351618</v>
       </c>
       <c r="N44" t="n">
-        <v>20148.83613138522</v>
+        <v>332.4752372202093</v>
       </c>
       <c r="O44" t="n">
-        <v>68.59125263288317</v>
+        <v>64.60672738795091</v>
       </c>
       <c r="P44" t="n">
-        <v>1041.071428571429</v>
+        <v>13.93928527832031</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.405719122181247</v>
+        <v>3.540585432085329</v>
       </c>
       <c r="R44" t="n">
-        <v>58518.3</v>
+        <v>6749220.9</v>
       </c>
       <c r="S44" t="n">
-        <v>1.125818760968791</v>
+        <v>1.107384705692475</v>
       </c>
       <c r="T44" t="n">
-        <v>24125</v>
+        <v>403.25</v>
       </c>
       <c r="U44" t="n">
-        <v>13498</v>
+        <v>191.3099975585938</v>
       </c>
       <c r="V44" t="n">
-        <v>-2.051813471502591</v>
+        <v>-2.368254877363608</v>
       </c>
       <c r="W44" t="n">
-        <v>75.06297229219143</v>
+        <v>105.7916560719469</v>
       </c>
       <c r="X44" t="n">
-        <v>31.80315981760629</v>
+        <v>46.94186391045708</v>
       </c>
       <c r="Y44" t="b">
         <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>18871</v>
+        <v>322.7000122070312</v>
       </c>
       <c r="AA44" t="n">
-        <v>24125</v>
+        <v>403.25</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
@@ -7211,17 +7215,17 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>PTCIL.NS</t>
+          <t>REDINGTON.NS</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>PTC Industries Limited</t>
+          <t>Redington Limited</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr"/>
@@ -7246,13 +7250,13 @@
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP44" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.1040134482034041</v>
+        <v>0.1345068703235035</v>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
@@ -7263,90 +7267,90 @@
         <v>143</v>
       </c>
       <c r="AT44" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>408</v>
+        <v>935</v>
       </c>
       <c r="B45" t="n">
-        <v>416.5</v>
+        <v>975</v>
       </c>
       <c r="C45" t="n">
-        <v>406</v>
+        <v>910</v>
       </c>
       <c r="D45" t="n">
-        <v>412.5499877929688</v>
+        <v>961.1500244140625</v>
       </c>
       <c r="E45" t="n">
-        <v>3209425</v>
+        <v>1471659</v>
       </c>
       <c r="F45" t="n">
-        <v>410.7999877929688</v>
+        <v>939.9000244140625</v>
       </c>
       <c r="G45" t="n">
-        <v>0.425998065238975</v>
+        <v>2.260878758168694</v>
       </c>
       <c r="H45" t="n">
-        <v>393.4124984741211</v>
+        <v>894.7700012207031</v>
       </c>
       <c r="I45" t="n">
-        <v>381.5749987792969</v>
+        <v>755.5639990234375</v>
       </c>
       <c r="J45" t="n">
-        <v>364.7274996948242</v>
+        <v>630.4514990234375</v>
       </c>
       <c r="K45" t="n">
-        <v>336.3727499389648</v>
+        <v>481.6102493286133</v>
       </c>
       <c r="L45" t="n">
-        <v>405.8323899746489</v>
+        <v>940.2757292035946</v>
       </c>
       <c r="M45" t="n">
-        <v>396.9724348712864</v>
+        <v>894.136226087591</v>
       </c>
       <c r="N45" t="n">
-        <v>383.5323839307324</v>
+        <v>783.9646046089808</v>
       </c>
       <c r="O45" t="n">
-        <v>65.29366249181774</v>
+        <v>66.624596028447</v>
       </c>
       <c r="P45" t="n">
-        <v>8.960715157645089</v>
+        <v>43.80000523158482</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.172031371418164</v>
+        <v>4.557041473133836</v>
       </c>
       <c r="R45" t="n">
-        <v>3376517.2</v>
+        <v>1276542.5</v>
       </c>
       <c r="S45" t="n">
-        <v>0.950513446222042</v>
+        <v>1.152847633353374</v>
       </c>
       <c r="T45" t="n">
-        <v>420.3999938964844</v>
+        <v>980.0999755859375</v>
       </c>
       <c r="U45" t="n">
-        <v>261.6000061035156</v>
+        <v>259.5</v>
       </c>
       <c r="V45" t="n">
-        <v>-1.867270746309416</v>
+        <v>-1.933471242109364</v>
       </c>
       <c r="W45" t="n">
-        <v>57.70259104264773</v>
+        <v>270.3853658628372</v>
       </c>
       <c r="X45" t="n">
-        <v>22.64667333124528</v>
+        <v>99.57009340103322</v>
       </c>
       <c r="Y45" t="b">
         <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>375</v>
+        <v>802.3499755859375</v>
       </c>
       <c r="AA45" t="n">
-        <v>420.3999938964844</v>
+        <v>980.0999755859375</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -7365,17 +7369,17 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>RBLBANK.NS</t>
+          <t>SHILPAMED.NS</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>RBL Bank Limited</t>
+          <t>Shilpa Medicare Limited</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr"/>
@@ -7400,13 +7404,13 @@
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP45" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.2090548243796112</v>
+        <v>0.1193321495283998</v>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
@@ -7417,90 +7421,90 @@
         <v>143</v>
       </c>
       <c r="AT45" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>395.8500061035156</v>
+        <v>888</v>
       </c>
       <c r="B46" t="n">
-        <v>396.8500061035156</v>
+        <v>905</v>
       </c>
       <c r="C46" t="n">
-        <v>384.2000122070312</v>
+        <v>859.9500122070312</v>
       </c>
       <c r="D46" t="n">
-        <v>393.7000122070312</v>
+        <v>897.4500122070312</v>
       </c>
       <c r="E46" t="n">
-        <v>7473984</v>
+        <v>168282</v>
       </c>
       <c r="F46" t="n">
-        <v>392</v>
+        <v>893.8499755859375</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4336765834263456</v>
+        <v>0.402756247628</v>
       </c>
       <c r="H46" t="n">
-        <v>360.9474990844727</v>
+        <v>852.4075012207031</v>
       </c>
       <c r="I46" t="n">
-        <v>325.4839990234375</v>
+        <v>772.2799987792969</v>
       </c>
       <c r="J46" t="n">
-        <v>282.1428994750976</v>
+        <v>685.4000009155274</v>
       </c>
       <c r="K46" t="n">
-        <v>267.9290991210938</v>
+        <v>579.626251525879</v>
       </c>
       <c r="L46" t="n">
-        <v>377.4684592602789</v>
+        <v>884.1960185966466</v>
       </c>
       <c r="M46" t="n">
-        <v>363.4923475351618</v>
+        <v>855.3830089081853</v>
       </c>
       <c r="N46" t="n">
-        <v>332.4752372202093</v>
+        <v>787.1814356845746</v>
       </c>
       <c r="O46" t="n">
-        <v>64.60672738795091</v>
+        <v>68.27585757403105</v>
       </c>
       <c r="P46" t="n">
-        <v>13.93928527832031</v>
+        <v>36.07857840401785</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.540585432085329</v>
+        <v>4.020121222717745</v>
       </c>
       <c r="R46" t="n">
-        <v>6749220.9</v>
+        <v>187045.45</v>
       </c>
       <c r="S46" t="n">
-        <v>1.107384705692475</v>
+        <v>0.899685076541557</v>
       </c>
       <c r="T46" t="n">
-        <v>403.25</v>
+        <v>915.9500122070312</v>
       </c>
       <c r="U46" t="n">
-        <v>191.3099975585938</v>
+        <v>399.7999877929688</v>
       </c>
       <c r="V46" t="n">
-        <v>-2.368254877363608</v>
+        <v>-2.019760877061756</v>
       </c>
       <c r="W46" t="n">
-        <v>105.7916560719469</v>
+        <v>124.4747472758214</v>
       </c>
       <c r="X46" t="n">
-        <v>46.94186391045708</v>
+        <v>54.83253386893264</v>
       </c>
       <c r="Y46" t="b">
         <v>1</v>
       </c>
       <c r="Z46" t="n">
-        <v>322.7000122070312</v>
+        <v>794.0499877929688</v>
       </c>
       <c r="AA46" t="n">
-        <v>403.25</v>
+        <v>915.9500122070312</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
@@ -7519,17 +7523,17 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>UNIPARTS</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>REDINGTON.NS</t>
+          <t>UNIPARTS.NS</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>Redington Limited</t>
+          <t>Uniparts India Limited</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr"/>
@@ -7554,13 +7558,13 @@
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP46" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.1345068703235035</v>
+        <v>0.1789167856084566</v>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
@@ -7571,90 +7575,88 @@
         <v>143</v>
       </c>
       <c r="AT46" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>935</v>
+        <v>5.179999828338623</v>
       </c>
       <c r="B47" t="n">
-        <v>975</v>
+        <v>5.179999828338623</v>
       </c>
       <c r="C47" t="n">
-        <v>910</v>
+        <v>5.179999828338623</v>
       </c>
       <c r="D47" t="n">
-        <v>961.1500244140625</v>
+        <v>5.179999828338623</v>
       </c>
       <c r="E47" t="n">
-        <v>1471659</v>
+        <v>85364</v>
       </c>
       <c r="F47" t="n">
-        <v>939.9000244140625</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="G47" t="n">
-        <v>2.260878758168694</v>
+        <v>1.96850208926016</v>
       </c>
       <c r="H47" t="n">
-        <v>894.7700012207031</v>
+        <v>4.302999973297119</v>
       </c>
       <c r="I47" t="n">
-        <v>755.5639990234375</v>
+        <v>3.263600006103516</v>
       </c>
       <c r="J47" t="n">
-        <v>630.4514990234375</v>
+        <v>2.656600006818771</v>
       </c>
       <c r="K47" t="n">
-        <v>481.6102493286133</v>
+        <v>2.188500003218651</v>
       </c>
       <c r="L47" t="n">
-        <v>940.2757292035946</v>
+        <v>4.787722044403476</v>
       </c>
       <c r="M47" t="n">
-        <v>894.136226087591</v>
+        <v>4.340786985476073</v>
       </c>
       <c r="N47" t="n">
-        <v>783.9646046089808</v>
-      </c>
-      <c r="O47" t="n">
-        <v>66.624596028447</v>
-      </c>
+        <v>3.568518653055021</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>43.80000523158482</v>
+        <v>0.09642853055681501</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.557041473133836</v>
+        <v>1.861554705644507</v>
       </c>
       <c r="R47" t="n">
-        <v>1276542.5</v>
+        <v>32985.95</v>
       </c>
       <c r="S47" t="n">
-        <v>1.152847633353374</v>
+        <v>2.587889692429656</v>
       </c>
       <c r="T47" t="n">
-        <v>980.0999755859375</v>
+        <v>5.179999828338623</v>
       </c>
       <c r="U47" t="n">
-        <v>259.5</v>
+        <v>1.299999952316284</v>
       </c>
       <c r="V47" t="n">
-        <v>-1.933471242109364</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>270.3853658628372</v>
+        <v>298.4615398722993</v>
       </c>
       <c r="X47" t="n">
-        <v>99.57009340103322</v>
+        <v>136.6917898432872</v>
       </c>
       <c r="Y47" t="b">
         <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>802.3499755859375</v>
+        <v>3.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>980.0999755859375</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
@@ -7663,27 +7665,27 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Insufficient Data</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>IMPEXFERRO</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>SHILPAMED.NS</t>
+          <t>IMPEXFERRO.NS</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Limited</t>
+          <t>Impex Ferro Tech Limited</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr"/>
@@ -7700,115 +7702,113 @@
       </c>
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>52W High Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP47" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.1193321495283998</v>
+        <v>-0.05952375883958259</v>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Confirmed price breakout | Volume is more than 2x average | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS47" t="n">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="AT47" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>888</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="B48" t="n">
-        <v>905</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="C48" t="n">
-        <v>859.9500122070312</v>
+        <v>3.319999933242798</v>
       </c>
       <c r="D48" t="n">
-        <v>897.4500122070312</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="E48" t="n">
-        <v>168282</v>
+        <v>2178546</v>
       </c>
       <c r="F48" t="n">
-        <v>893.8499755859375</v>
+        <v>3.269999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>0.402756247628</v>
+        <v>1.834860646162473</v>
       </c>
       <c r="H48" t="n">
-        <v>852.4075012207031</v>
+        <v>2.779500007629395</v>
       </c>
       <c r="I48" t="n">
-        <v>772.2799987792969</v>
+        <v>2.266599998474121</v>
       </c>
       <c r="J48" t="n">
-        <v>685.4000009155274</v>
+        <v>1.686199998855591</v>
       </c>
       <c r="K48" t="n">
-        <v>579.626251525879</v>
+        <v>1.422499998807907</v>
       </c>
       <c r="L48" t="n">
-        <v>884.1960185966466</v>
+        <v>3.085268005688187</v>
       </c>
       <c r="M48" t="n">
-        <v>855.3830089081853</v>
+        <v>2.832618148765642</v>
       </c>
       <c r="N48" t="n">
-        <v>787.1814356845746</v>
-      </c>
-      <c r="O48" t="n">
-        <v>68.27585757403105</v>
-      </c>
+        <v>2.36228866312997</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>36.07857840401785</v>
+        <v>0.06071427890232631</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.020121222717745</v>
+        <v>1.823251660461169</v>
       </c>
       <c r="R48" t="n">
-        <v>187045.45</v>
+        <v>475284.4</v>
       </c>
       <c r="S48" t="n">
-        <v>0.899685076541557</v>
+        <v>4.583668220543321</v>
       </c>
       <c r="T48" t="n">
-        <v>915.9500122070312</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="U48" t="n">
-        <v>399.7999877929688</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="V48" t="n">
-        <v>-2.019760877061756</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>124.4747472758214</v>
+        <v>389.7058659822885</v>
       </c>
       <c r="X48" t="n">
-        <v>54.83253386893264</v>
+        <v>134.0948981719988</v>
       </c>
       <c r="Y48" t="b">
         <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>794.0499877929688</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="AA48" t="n">
-        <v>915.9500122070312</v>
+        <v>3.269999980926514</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Insufficient Data</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>UNIPARTS</t>
+          <t>SUPREMEENG</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>UNIPARTS.NS</t>
+          <t>SUPREMEENG.NS</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Uniparts India Limited</t>
+          <t>Supreme Engineering Limited</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr"/>
@@ -7854,32 +7854,32 @@
       </c>
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>52W High Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP48" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.1789167856084566</v>
+        <v>-0.05940588450106899</v>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
+          <t>Strong price trend | Confirmed price breakout | Volume is more than 2x average | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
       <c r="AS48" t="n">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="AT48" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49">
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP49" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.4704104087787023</v>
@@ -8033,7 +8033,7 @@
         <v>207</v>
       </c>
       <c r="AT49" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50">
@@ -8170,10 +8170,10 @@
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP50" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.0374384236453202</v>
@@ -8187,7 +8187,7 @@
         <v>207</v>
       </c>
       <c r="AT50" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP51" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.5094339234633758</v>
@@ -8341,7 +8341,7 @@
         <v>207</v>
       </c>
       <c r="AT51" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP52" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.1327967806841046</v>
@@ -8495,7 +8495,7 @@
         <v>207</v>
       </c>
       <c r="AT52" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53">
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP53" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.1649587043541939</v>
@@ -8649,7 +8649,7 @@
         <v>207</v>
       </c>
       <c r="AT53" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP54" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.06165507251926288</v>
@@ -8803,7 +8803,7 @@
         <v>207</v>
       </c>
       <c r="AT54" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55">
@@ -8940,10 +8940,10 @@
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP55" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.2846299810246679</v>
@@ -8957,7 +8957,7 @@
         <v>207</v>
       </c>
       <c r="AT55" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP56" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ56" t="n">
         <v>-0.08489464915062693</v>
@@ -9111,7 +9111,7 @@
         <v>207</v>
       </c>
       <c r="AT56" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57">
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="AO57" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP57" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.3566183359157356</v>
@@ -9265,7 +9265,7 @@
         <v>207</v>
       </c>
       <c r="AT57" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58">
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="AO58" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP58" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.2086770762661636</v>
@@ -9419,7 +9419,7 @@
         <v>207</v>
       </c>
       <c r="AT58" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59">
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="AO59" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP59" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.6093453380549065</v>
@@ -9573,7 +9573,7 @@
         <v>207</v>
       </c>
       <c r="AT59" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60">
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="AO60" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP60" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.0756748538335015</v>
@@ -9727,7 +9727,7 @@
         <v>207</v>
       </c>
       <c r="AT60" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61">
@@ -9864,10 +9864,10 @@
         </is>
       </c>
       <c r="AO61" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP61" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.1966097556938559</v>
@@ -9881,7 +9881,7 @@
         <v>207</v>
       </c>
       <c r="AT61" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62">
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="AO62" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP62" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.1028685314284248</v>
@@ -10035,7 +10035,7 @@
         <v>304</v>
       </c>
       <c r="AT62" t="n">
-        <v>300</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="AO63" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP63" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.2254098360655738</v>
@@ -10189,7 +10189,7 @@
         <v>304</v>
       </c>
       <c r="AT63" t="n">
-        <v>300</v>
+        <v>231</v>
       </c>
     </row>
     <row r="64">
@@ -10326,10 +10326,10 @@
         </is>
       </c>
       <c r="AO64" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP64" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.09610150067312981</v>
@@ -10343,7 +10343,7 @@
         <v>304</v>
       </c>
       <c r="AT64" t="n">
-        <v>300</v>
+        <v>231</v>
       </c>
     </row>
     <row r="65">
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="AO65" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP65" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.04708222811671087</v>
@@ -10497,7 +10497,7 @@
         <v>304</v>
       </c>
       <c r="AT65" t="n">
-        <v>300</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66">
@@ -10634,10 +10634,10 @@
         </is>
       </c>
       <c r="AO66" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP66" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.1080645161290323</v>
@@ -10651,7 +10651,7 @@
         <v>304</v>
       </c>
       <c r="AT66" t="n">
-        <v>300</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67">
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="AO67" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP67" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.008756566489564967</v>
@@ -10805,7 +10805,7 @@
         <v>304</v>
       </c>
       <c r="AT67" t="n">
-        <v>300</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68">
@@ -10942,10 +10942,10 @@
         </is>
       </c>
       <c r="AO68" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP68" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.3297961176658163</v>
@@ -10959,7 +10959,7 @@
         <v>355</v>
       </c>
       <c r="AT68" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="69">
@@ -11096,10 +11096,10 @@
         </is>
       </c>
       <c r="AO69" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP69" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.4592586564429013</v>
@@ -11113,7 +11113,7 @@
         <v>355</v>
       </c>
       <c r="AT69" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="70">
@@ -11250,10 +11250,10 @@
         </is>
       </c>
       <c r="AO70" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP70" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.1239480542769203</v>
@@ -11267,7 +11267,7 @@
         <v>355</v>
       </c>
       <c r="AT70" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71">
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="AO71" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP71" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.6845238095238095</v>
@@ -11421,7 +11421,7 @@
         <v>355</v>
       </c>
       <c r="AT71" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72">
@@ -11558,10 +11558,10 @@
         </is>
       </c>
       <c r="AO72" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP72" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.2013654792066472</v>
@@ -11575,7 +11575,7 @@
         <v>355</v>
       </c>
       <c r="AT72" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73">
@@ -11712,10 +11712,10 @@
         </is>
       </c>
       <c r="AO73" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP73" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.08088235294117647</v>
@@ -11729,7 +11729,7 @@
         <v>445</v>
       </c>
       <c r="AT73" t="n">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="74">
@@ -11866,10 +11866,10 @@
         </is>
       </c>
       <c r="AO74" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP74" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.02201473014304648</v>
@@ -11883,7 +11883,7 @@
         <v>445</v>
       </c>
       <c r="AT74" t="n">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75">
@@ -12020,10 +12020,10 @@
         </is>
       </c>
       <c r="AO75" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP75" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.1234516336096472</v>
@@ -12037,7 +12037,7 @@
         <v>445</v>
       </c>
       <c r="AT75" t="n">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76">
@@ -12174,10 +12174,10 @@
         </is>
       </c>
       <c r="AO76" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP76" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.2289803220035778</v>
@@ -12191,7 +12191,7 @@
         <v>445</v>
       </c>
       <c r="AT76" t="n">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="77">
@@ -12328,10 +12328,10 @@
         </is>
       </c>
       <c r="AO77" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP77" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.08477461965460527</v>
@@ -12345,7 +12345,7 @@
         <v>445</v>
       </c>
       <c r="AT77" t="n">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="78">
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="AO78" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP78" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ78" t="n">
         <v>-0.0593584185721464</v>
@@ -12497,7 +12497,7 @@
         <v>493</v>
       </c>
       <c r="AT78" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="79">
@@ -12634,10 +12634,10 @@
         </is>
       </c>
       <c r="AO79" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP79" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.08095598598591533</v>
@@ -12651,7 +12651,7 @@
         <v>493</v>
       </c>
       <c r="AT79" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="80">
@@ -12788,10 +12788,10 @@
         </is>
       </c>
       <c r="AO80" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP80" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.2143987341772152</v>
@@ -12805,7 +12805,7 @@
         <v>493</v>
       </c>
       <c r="AT80" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="81">
@@ -12940,10 +12940,10 @@
         </is>
       </c>
       <c r="AO81" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP81" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ81" t="n">
         <v>-0.04921967000807589</v>
@@ -12957,7 +12957,7 @@
         <v>565</v>
       </c>
       <c r="AT81" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="82">
@@ -13092,10 +13092,10 @@
         </is>
       </c>
       <c r="AO82" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP82" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ82" t="n">
         <v>-0.1663868153821396</v>
@@ -13109,7 +13109,7 @@
         <v>565</v>
       </c>
       <c r="AT82" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="83">
@@ -13246,10 +13246,10 @@
         </is>
       </c>
       <c r="AO83" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP83" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.1068703579351245</v>
@@ -13263,7 +13263,7 @@
         <v>565</v>
       </c>
       <c r="AT83" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="84">
@@ -13400,10 +13400,10 @@
         </is>
       </c>
       <c r="AO84" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP84" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.1509220323575331</v>
@@ -13417,7 +13417,7 @@
         <v>565</v>
       </c>
       <c r="AT84" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="85">
@@ -13552,10 +13552,10 @@
         </is>
       </c>
       <c r="AO85" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP85" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ85" t="n">
         <v>0</v>
@@ -13569,7 +13569,7 @@
         <v>638</v>
       </c>
       <c r="AT85" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>

--- a/output/exports/52w_high.xlsx
+++ b/output/exports/52w_high.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT85"/>
+  <dimension ref="A1:BJ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>ATR_Percent</t>
+          <t>ATR_Pct</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -629,20 +629,100 @@
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>entry_low</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>entry_high</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>entry_price</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>target_1</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>target_2</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>risk_points</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>reward_1_points</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>reward_2_points</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>risk_reward_1</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>risk_reward_2</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>trade_plan_type</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>trade_plan_status</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>trade_plan_reason</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>invalidation</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
           <t>risk_reward</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>setup_reasons</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>trade_plan_quality</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
         <is>
           <t>technical_rank</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
@@ -788,17 +868,75 @@
         <v>86</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.1860642598434397</v>
-      </c>
-      <c r="AR2" t="inlineStr">
+        <v>1849.47</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1871.57</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1849.47</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1776.86</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1975.76</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2070.47</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>126.29</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>221</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Below ₹1776.86</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS2" t="n">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI2" t="n">
         <v>2</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BJ2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -942,17 +1080,75 @@
         <v>86</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.07027007800283061</v>
-      </c>
-      <c r="AR3" t="inlineStr">
+        <v>21.19</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>Below ₹19.71</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG3" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS3" t="n">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI3" t="n">
         <v>2</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BJ3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1096,17 +1292,75 @@
         <v>86</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.1334990530806877</v>
-      </c>
-      <c r="AR4" t="inlineStr">
+        <v>2332.35</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2363.51</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2332.35</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2229.98</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2510.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2643.93</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>102.37</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>178.04</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>311.58</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>Below ₹2229.98</t>
+        </is>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG4" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS4" t="n">
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI4" t="n">
         <v>2</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BJ4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1250,17 +1504,75 @@
         <v>81</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.1202894372010538</v>
-      </c>
-      <c r="AR5" t="inlineStr">
+        <v>396.16</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>402.71</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>396.16</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>433.59</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>461.66</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>Below ₹374.64</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG5" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS5" t="n">
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI5" t="n">
         <v>13</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BJ5" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1404,17 +1716,75 @@
         <v>81</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.206133018539621</v>
-      </c>
-      <c r="AR6" t="inlineStr">
+        <v>26.22</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>Below ₹24.81</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG6" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS6" t="n">
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI6" t="n">
         <v>13</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BJ6" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1558,17 +1928,75 @@
         <v>81</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.03697762763578034</v>
-      </c>
-      <c r="AR7" t="inlineStr">
+        <v>918.75</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>927.86</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>918.75</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>888.8200000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>970.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1009.84</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>52.05</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>Below ₹888.82</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG7" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS7" t="n">
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI7" t="n">
         <v>13</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BJ7" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1712,17 +2140,75 @@
         <v>81</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.04000019929846939</v>
-      </c>
-      <c r="AR8" t="inlineStr">
+        <v>741.77</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>750.58</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>741.77</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>712.84</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>792.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>829.84</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>88.06</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>Below ₹712.84</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG8" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS8" t="n">
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI8" t="n">
         <v>13</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BJ8" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1866,17 +2352,75 @@
         <v>81</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.04560891802842767</v>
-      </c>
-      <c r="AR9" t="inlineStr">
+        <v>521.78</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>528.28</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>521.78</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>500.45</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>558.89</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>586.72</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>Below ₹500.45</t>
+        </is>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG9" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS9" t="n">
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI9" t="n">
         <v>41</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BJ9" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2020,17 +2564,75 @@
         <v>80</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.06898572389981884</v>
-      </c>
-      <c r="AR10" t="inlineStr">
+        <v>818.3</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>831.13</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>818.3</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>776.14</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>891.61</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>946.6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>73.31</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>Below ₹776.14</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG10" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS10" t="n">
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI10" t="n">
         <v>22</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BJ10" t="n">
         <v>27</v>
       </c>
     </row>
@@ -2174,17 +2776,75 @@
         <v>79</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.138098311939258</v>
-      </c>
-      <c r="AR11" t="inlineStr">
+        <v>1810.07</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1833.55</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1810.07</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1732.89</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1944.28</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2044.94</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>77.17</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>134.21</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>234.88</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>Below ₹1732.89</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG11" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS11" t="n">
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI11" t="n">
         <v>24</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BJ11" t="n">
         <v>29</v>
       </c>
     </row>
@@ -2328,17 +2988,75 @@
         <v>78</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.04112183090928875</v>
-      </c>
-      <c r="AR12" t="inlineStr">
+        <v>242.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>245.45</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>260.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>274.76</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>Below ₹231.50</t>
+        </is>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG12" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS12" t="n">
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI12" t="n">
         <v>45</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BJ12" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2482,17 +3200,75 @@
         <v>77</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.2870200899278381</v>
-      </c>
-      <c r="AR13" t="inlineStr">
+        <v>20.13</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>Below ₹19.14</t>
+        </is>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG13" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS13" t="n">
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI13" t="n">
         <v>33</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BJ13" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2636,17 +3412,75 @@
         <v>77</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.3415007451803956</v>
-      </c>
-      <c r="AR14" t="inlineStr">
+        <v>1032.48</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1051.08</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1032.48</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>971.33</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1138.81</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1218.56</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>106.34</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>186.09</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>Below ₹971.33</t>
+        </is>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG14" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS14" t="n">
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI14" t="n">
         <v>33</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BJ14" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2790,17 +3624,75 @@
         <v>77</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.1264204545454546</v>
-      </c>
-      <c r="AR15" t="inlineStr">
+        <v>492.72</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>500.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>492.72</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>468.15</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>535.45</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>567.49</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>74.78</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>Below ₹468.15</t>
+        </is>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG15" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS15" t="n">
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI15" t="n">
         <v>33</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BJ15" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2944,17 +3836,75 @@
         <v>77</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.1479690512532134</v>
-      </c>
-      <c r="AR16" t="inlineStr">
+        <v>3182.1</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3230.68</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3182.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3022.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3459.67</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3667.85</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>277.57</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>485.75</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>Below ₹3022.50</t>
+        </is>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG16" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS16" t="n">
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI16" t="n">
         <v>33</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BJ16" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3098,17 +4048,75 @@
         <v>77</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.1449998450278989</v>
-      </c>
-      <c r="AR17" t="inlineStr">
+        <v>38.25</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>Below ₹36.60</t>
+        </is>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG17" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS17" t="n">
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI17" t="n">
         <v>33</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BJ17" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3252,17 +4260,75 @@
         <v>77</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0.1685290987967586</v>
-      </c>
-      <c r="AR18" t="inlineStr">
+        <v>399.63</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>405.76</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>399.63</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>434.68</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>460.97</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>Below ₹379.48</t>
+        </is>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG18" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS18" t="n">
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI18" t="n">
         <v>33</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BJ18" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3406,17 +4472,75 @@
         <v>77</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.1478930944683908</v>
-      </c>
-      <c r="AR19" t="inlineStr">
+        <v>434.7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>440.29</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>416.31</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>466.67</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>490.65</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>Below ₹416.31</t>
+        </is>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG19" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS19" t="n">
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI19" t="n">
         <v>54</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BJ19" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3560,17 +4684,75 @@
         <v>77</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.1011613601073889</v>
-      </c>
-      <c r="AR20" t="inlineStr">
+        <v>234.73</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>238.77</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>234.73</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>221.45</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>257.83</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>Below ₹221.45</t>
+        </is>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG20" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS20" t="n">
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI20" t="n">
         <v>54</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BJ20" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3714,17 +4896,75 @@
         <v>76</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-0.02595494449136814</v>
-      </c>
-      <c r="AR21" t="inlineStr">
+        <v>738.24</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>750.48</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>738.24</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>698.04</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>808.17</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>860.61</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>122.36</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>Below ₹698.04</t>
+        </is>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG21" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS21" t="n">
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI21" t="n">
         <v>59</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BJ21" t="n">
         <v>48</v>
       </c>
     </row>
@@ -3868,17 +5108,75 @@
         <v>76</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-0.03036922132176373</v>
-      </c>
-      <c r="AR22" t="inlineStr">
+        <v>216.37</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>219.56</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>216.37</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>205.87</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>234.62</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>248.31</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>31.94</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>Below ₹205.87</t>
+        </is>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG22" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS22" t="n">
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI22" t="n">
         <v>59</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="BJ22" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4022,17 +5320,75 @@
         <v>75</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.09871266242138327</v>
-      </c>
-      <c r="AR23" t="inlineStr">
+        <v>9.09</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>Below ₹8.47</t>
+        </is>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG23" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS23" t="n">
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI23" t="n">
         <v>67</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="BJ23" t="n">
         <v>56</v>
       </c>
     </row>
@@ -4176,17 +5532,75 @@
         <v>75</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.1366635564233045</v>
-      </c>
-      <c r="AR24" t="inlineStr">
+        <v>381.53</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>387.42</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>381.53</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>415.22</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>440.49</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>Below ₹362.15</t>
+        </is>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG24" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS24" t="n">
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI24" t="n">
         <v>67</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="BJ24" t="n">
         <v>56</v>
       </c>
     </row>
@@ -4330,17 +5744,75 @@
         <v>73</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-0.007910429205460735</v>
-      </c>
-      <c r="AR25" t="inlineStr">
+        <v>1248.87</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1269.1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1248.87</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1182.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1364.48</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1451.18</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>202.31</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>Below ₹1182.40</t>
+        </is>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG25" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS25" t="n">
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI25" t="n">
         <v>86</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="BJ25" t="n">
         <v>67</v>
       </c>
     </row>
@@ -4484,17 +5956,75 @@
         <v>73</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-0.1494417219424637</v>
-      </c>
-      <c r="AR26" t="inlineStr">
+        <v>877.85</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>891.67</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>877.85</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>832.45</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>956.8099999999999</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1016.03</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>78.95999999999999</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>138.18</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>Below ₹832.45</t>
+        </is>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG26" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS26" t="n">
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI26" t="n">
         <v>86</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="BJ26" t="n">
         <v>67</v>
       </c>
     </row>
@@ -4638,17 +6168,75 @@
         <v>73</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.00262930156476652</v>
-      </c>
-      <c r="AR27" t="inlineStr">
+        <v>764.8200000000001</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>777.12</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>764.8200000000001</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>724.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>835.12</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>887.85</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>Below ₹724.40</t>
+        </is>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG27" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS27" t="n">
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI27" t="n">
         <v>86</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="BJ27" t="n">
         <v>67</v>
       </c>
     </row>
@@ -4792,17 +6380,75 @@
         <v>73</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-0.03996406842261901</v>
-      </c>
-      <c r="AR28" t="inlineStr">
+        <v>2768.56</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2811.87</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2768.56</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2626.26</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3016.05</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>3201.66</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>247.49</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>433.1</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>Below ₹2626.26</t>
+        </is>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG28" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS28" t="n">
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI28" t="n">
         <v>86</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="BJ28" t="n">
         <v>67</v>
       </c>
     </row>
@@ -4946,17 +6592,75 @@
         <v>73</v>
       </c>
       <c r="AQ29" t="n">
-        <v>-0.04229064593422944</v>
-      </c>
-      <c r="AR29" t="inlineStr">
+        <v>130.92</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>133.31</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>130.92</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>123.08</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>144.56</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>154.79</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>Below ₹123.08</t>
+        </is>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG29" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS29" t="n">
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI29" t="n">
         <v>86</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="BJ29" t="n">
         <v>67</v>
       </c>
     </row>
@@ -5100,17 +6804,75 @@
         <v>73</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.0694281728976802</v>
-      </c>
-      <c r="AR30" t="inlineStr">
+        <v>1142.41</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1160.39</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1142.41</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1083.31</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1245.19</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1322.27</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>102.78</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>179.86</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
+        <is>
+          <t>Below ₹1083.31</t>
+        </is>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG30" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS30" t="n">
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI30" t="n">
         <v>86</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="BJ30" t="n">
         <v>67</v>
       </c>
     </row>
@@ -5254,17 +7016,75 @@
         <v>72</v>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.1703153251137194</v>
-      </c>
-      <c r="AR31" t="inlineStr">
+        <v>472.01</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>479.02</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>472.01</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>448.95</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>512.1</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>542.17</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>Below ₹448.95</t>
+        </is>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG31" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS31" t="n">
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI31" t="n">
         <v>54</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="BJ31" t="n">
         <v>90</v>
       </c>
     </row>
@@ -5408,17 +7228,75 @@
         <v>72</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.4126834032012195</v>
-      </c>
-      <c r="AR32" t="inlineStr">
+        <v>1725.76</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1746.19</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1725.76</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1658.61</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1842.53</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1930.11</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>67.14</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>116.77</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>204.35</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
+        <is>
+          <t>Below ₹1658.61</t>
+        </is>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG32" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS32" t="n">
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI32" t="n">
         <v>104</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="BJ32" t="n">
         <v>90</v>
       </c>
     </row>
@@ -5562,17 +7440,75 @@
         <v>72</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.1561373197115385</v>
-      </c>
-      <c r="AR33" t="inlineStr">
+        <v>999.1900000000001</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1014.58</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>999.1900000000001</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>948.64</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1087.12</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1153.07</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>153.88</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>Below ₹948.64</t>
+        </is>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG33" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS33" t="n">
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI33" t="n">
         <v>104</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="BJ33" t="n">
         <v>90</v>
       </c>
     </row>
@@ -5716,17 +7652,75 @@
         <v>72</v>
       </c>
       <c r="AQ34" t="n">
-        <v>-0.03796168640139019</v>
-      </c>
-      <c r="AR34" t="inlineStr">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>86.08</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>81.65000000000001</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
+        <is>
+          <t>Below ₹81.65</t>
+        </is>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG34" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS34" t="n">
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI34" t="n">
         <v>104</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="BJ34" t="n">
         <v>90</v>
       </c>
     </row>
@@ -5870,17 +7864,75 @@
         <v>72</v>
       </c>
       <c r="AQ35" t="n">
-        <v>-0.0003375054414772977</v>
-      </c>
-      <c r="AR35" t="inlineStr">
+        <v>904.21</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>920</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>904.21</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>852.36</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>994.4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1062.04</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>90.19</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>157.83</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>Below ₹852.36</t>
+        </is>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG35" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS35" t="n">
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI35" t="n">
         <v>104</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="BJ35" t="n">
         <v>90</v>
       </c>
     </row>
@@ -6024,17 +8076,75 @@
         <v>72</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.2266951152490867</v>
-      </c>
-      <c r="AR36" t="inlineStr">
+        <v>1662.68</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1685.72</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1662.68</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1586.96</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1794.36</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1893.13</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>131.69</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>230.45</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>Below ₹1586.96</t>
+        </is>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG36" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS36" t="n">
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI36" t="n">
         <v>104</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="BJ36" t="n">
         <v>90</v>
       </c>
     </row>
@@ -6178,17 +8288,75 @@
         <v>72</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.314136025270464</v>
-      </c>
-      <c r="AR37" t="inlineStr">
+        <v>901.6799999999999</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>914.95</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>901.6799999999999</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>858.1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>977.48</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1034.32</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>43.58</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>132.64</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>Below ₹858.10</t>
+        </is>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG37" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS37" t="n">
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI37" t="n">
         <v>104</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="BJ37" t="n">
         <v>90</v>
       </c>
     </row>
@@ -6332,17 +8500,75 @@
         <v>70</v>
       </c>
       <c r="AQ38" t="n">
-        <v>-0.0448275366854716</v>
-      </c>
-      <c r="AR38" t="inlineStr">
+        <v>2058.05</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2089.9</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2058.05</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1953.41</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>2240.03</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2376.52</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>104.64</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>181.99</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>318.48</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>Below ₹1953.41</t>
+        </is>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG38" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS38" t="n">
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI38" t="n">
         <v>67</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="BJ38" t="n">
         <v>107</v>
       </c>
     </row>
@@ -6486,17 +8712,75 @@
         <v>70</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.09880615213747107</v>
-      </c>
-      <c r="AR39" t="inlineStr">
+        <v>101.95</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>103.48</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>110.73</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>117.31</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>Below ₹96.90</t>
+        </is>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG39" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS39" t="n">
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI39" t="n">
         <v>131</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="BJ39" t="n">
         <v>107</v>
       </c>
     </row>
@@ -6640,17 +8924,75 @@
         <v>70</v>
       </c>
       <c r="AQ40" t="n">
-        <v>-0.07014028914032767</v>
-      </c>
-      <c r="AR40" t="inlineStr">
+        <v>1989.83</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2008.55</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1989.83</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1928.29</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2096.84</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2177.1</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>107.01</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>187.28</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>Below ₹1928.29</t>
+        </is>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG40" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS40" t="n">
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI40" t="n">
         <v>131</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="BJ40" t="n">
         <v>107</v>
       </c>
     </row>
@@ -6794,17 +9136,75 @@
         <v>69</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.1829926573775748</v>
-      </c>
-      <c r="AR41" t="inlineStr">
+        <v>1484.67</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1496.51</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1484.67</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1445.77</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1552.33</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1603.07</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>Below ₹1445.77</t>
+        </is>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG41" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS41" t="n">
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI41" t="n">
         <v>143</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="BJ41" t="n">
         <v>129</v>
       </c>
     </row>
@@ -6948,17 +9348,75 @@
         <v>69</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.1040134482034041</v>
-      </c>
-      <c r="AR42" t="inlineStr">
+        <v>24281.16</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>24645.54</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>24281.16</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>23083.93</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>26363.3</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>27924.91</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1197.23</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>2082.14</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>3643.75</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
+        <is>
+          <t>Below ₹23083.93</t>
+        </is>
+      </c>
+      <c r="BF42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG42" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS42" t="n">
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI42" t="n">
         <v>143</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="BJ42" t="n">
         <v>129</v>
       </c>
     </row>
@@ -7102,17 +9560,75 @@
         <v>69</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.2090548243796112</v>
-      </c>
-      <c r="AR43" t="inlineStr">
+        <v>421.74</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>424.88</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>421.74</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>411.44</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>439.67</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>453.11</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>Below ₹411.44</t>
+        </is>
+      </c>
+      <c r="BF43" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG43" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS43" t="n">
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI43" t="n">
         <v>143</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="BJ43" t="n">
         <v>129</v>
       </c>
     </row>
@@ -7256,17 +9772,75 @@
         <v>69</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.1345068703235035</v>
-      </c>
-      <c r="AR44" t="inlineStr">
+        <v>405.34</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>410.22</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>405.34</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>389.31</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>433.22</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>454.13</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE44" t="inlineStr">
+        <is>
+          <t>Below ₹389.31</t>
+        </is>
+      </c>
+      <c r="BF44" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG44" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS44" t="n">
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI44" t="n">
         <v>143</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="BJ44" t="n">
         <v>129</v>
       </c>
     </row>
@@ -7410,17 +9984,75 @@
         <v>69</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.1193321495283998</v>
-      </c>
-      <c r="AR45" t="inlineStr">
+        <v>986.67</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1002</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>986.67</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>936.3</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1074.27</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1139.97</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>153.3</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>Below ₹936.30</t>
+        </is>
+      </c>
+      <c r="BF45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG45" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS45" t="n">
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI45" t="n">
         <v>143</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="BJ45" t="n">
         <v>129</v>
       </c>
     </row>
@@ -7564,17 +10196,75 @@
         <v>69</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.1789167856084566</v>
-      </c>
-      <c r="AR46" t="inlineStr">
+        <v>921.36</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>933.99</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>921.36</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>879.87</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>993.52</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1047.64</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>126.28</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE46" t="inlineStr">
+        <is>
+          <t>Below ₹879.87</t>
+        </is>
+      </c>
+      <c r="BF46" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG46" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS46" t="n">
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI46" t="n">
         <v>143</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="BJ46" t="n">
         <v>129</v>
       </c>
     </row>
@@ -7716,17 +10406,75 @@
         <v>68</v>
       </c>
       <c r="AQ47" t="n">
-        <v>-0.05952375883958259</v>
-      </c>
-      <c r="AR47" t="inlineStr">
+        <v>5.29</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr">
+        <is>
+          <t>Below ₹5.18</t>
+        </is>
+      </c>
+      <c r="BF47" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG47" t="inlineStr">
         <is>
           <t>Strong price trend | Confirmed price breakout | Volume is more than 2x average | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS47" t="n">
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI47" t="n">
         <v>86</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="BJ47" t="n">
         <v>137</v>
       </c>
     </row>
@@ -7868,17 +10616,75 @@
         <v>68</v>
       </c>
       <c r="AQ48" t="n">
-        <v>-0.05940588450106899</v>
-      </c>
-      <c r="AR48" t="inlineStr">
+        <v>3.4</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE48" t="inlineStr">
+        <is>
+          <t>Below ₹3.33</t>
+        </is>
+      </c>
+      <c r="BF48" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG48" t="inlineStr">
         <is>
           <t>Strong price trend | Confirmed price breakout | Volume is more than 2x average | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS48" t="n">
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI48" t="n">
         <v>86</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="BJ48" t="n">
         <v>137</v>
       </c>
     </row>
@@ -8022,17 +10828,75 @@
         <v>66</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.4704104087787023</v>
-      </c>
-      <c r="AR49" t="inlineStr">
+        <v>2247.93</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2261.75</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2247.93</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>2202.49</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>2326.94</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>2386.2</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>79.01000000000001</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>138.27</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE49" t="inlineStr">
+        <is>
+          <t>Below ₹2202.49</t>
+        </is>
+      </c>
+      <c r="BF49" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG49" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS49" t="n">
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI49" t="n">
         <v>207</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="BJ49" t="n">
         <v>189</v>
       </c>
     </row>
@@ -8176,17 +11040,75 @@
         <v>66</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.0374384236453202</v>
-      </c>
-      <c r="AR50" t="inlineStr">
+        <v>2392.06</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2420.19</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2392.06</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2299.63</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>2552.8</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2673.36</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>281.3</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE50" t="inlineStr">
+        <is>
+          <t>Below ₹2299.63</t>
+        </is>
+      </c>
+      <c r="BF50" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG50" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS50" t="n">
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI50" t="n">
         <v>207</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="BJ50" t="n">
         <v>189</v>
       </c>
     </row>
@@ -8330,17 +11252,75 @@
         <v>66</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.5094339234633758</v>
-      </c>
-      <c r="AR51" t="inlineStr">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr">
+        <is>
+          <t>Below ₹87.10</t>
+        </is>
+      </c>
+      <c r="BF51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG51" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS51" t="n">
+      <c r="BH51" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI51" t="n">
         <v>207</v>
       </c>
-      <c r="AT51" t="n">
+      <c r="BJ51" t="n">
         <v>189</v>
       </c>
     </row>
@@ -8484,17 +11464,75 @@
         <v>66</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.1327967806841046</v>
-      </c>
-      <c r="AR52" t="inlineStr">
+        <v>2007.81</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>2022.53</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2007.81</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>1959.44</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>2091.94</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2155.03</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>84.13</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>147.23</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE52" t="inlineStr">
+        <is>
+          <t>Below ₹1959.44</t>
+        </is>
+      </c>
+      <c r="BF52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG52" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS52" t="n">
+      <c r="BH52" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI52" t="n">
         <v>207</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="BJ52" t="n">
         <v>189</v>
       </c>
     </row>
@@ -8638,17 +11676,75 @@
         <v>66</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.1649587043541939</v>
-      </c>
-      <c r="AR53" t="inlineStr">
+        <v>321.77</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>325.9</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>321.77</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>308.21</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>345.35</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>363.04</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr">
+        <is>
+          <t>Below ₹308.21</t>
+        </is>
+      </c>
+      <c r="BF53" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG53" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS53" t="n">
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI53" t="n">
         <v>207</v>
       </c>
-      <c r="AT53" t="n">
+      <c r="BJ53" t="n">
         <v>189</v>
       </c>
     </row>
@@ -8792,17 +11888,75 @@
         <v>66</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.06165507251926288</v>
-      </c>
-      <c r="AR54" t="inlineStr">
+        <v>603.61</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>612.02</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>603.61</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>575.96</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>651.6799999999999</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>687.74</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>84.14</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
+        <is>
+          <t>Below ₹575.96</t>
+        </is>
+      </c>
+      <c r="BF54" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG54" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS54" t="n">
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI54" t="n">
         <v>207</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="BJ54" t="n">
         <v>189</v>
       </c>
     </row>
@@ -8946,17 +12100,75 @@
         <v>66</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.2846299810246679</v>
-      </c>
-      <c r="AR55" t="inlineStr">
+        <v>6373.23</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>6434.43</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>6373.23</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>6172.14</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>6722.94</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>6985.23</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>201.09</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>349.71</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>612</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
+        <is>
+          <t>Below ₹6172.14</t>
+        </is>
+      </c>
+      <c r="BF55" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG55" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS55" t="n">
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI55" t="n">
         <v>207</v>
       </c>
-      <c r="AT55" t="n">
+      <c r="BJ55" t="n">
         <v>189</v>
       </c>
     </row>
@@ -9100,17 +12312,75 @@
         <v>66</v>
       </c>
       <c r="AQ56" t="n">
-        <v>-0.08489464915062693</v>
-      </c>
-      <c r="AR56" t="inlineStr">
+        <v>121.57</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>123.46</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>121.57</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>115.37</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>132.36</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr">
+        <is>
+          <t>Below ₹115.37</t>
+        </is>
+      </c>
+      <c r="BF56" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG56" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS56" t="n">
+      <c r="BH56" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI56" t="n">
         <v>207</v>
       </c>
-      <c r="AT56" t="n">
+      <c r="BJ56" t="n">
         <v>189</v>
       </c>
     </row>
@@ -9254,17 +12524,75 @@
         <v>66</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.3566183359157356</v>
-      </c>
-      <c r="AR57" t="inlineStr">
+        <v>381.72</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>385.74</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>381.72</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>421.94</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE57" t="inlineStr">
+        <is>
+          <t>Below ₹368.51</t>
+        </is>
+      </c>
+      <c r="BF57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG57" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS57" t="n">
+      <c r="BH57" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI57" t="n">
         <v>207</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="BJ57" t="n">
         <v>189</v>
       </c>
     </row>
@@ -9408,17 +12736,75 @@
         <v>66</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.2086770762661636</v>
-      </c>
-      <c r="AR58" t="inlineStr">
+        <v>350.66</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>353.25</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>350.66</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>342.15</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>365.45</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE58" t="inlineStr">
+        <is>
+          <t>Below ₹342.15</t>
+        </is>
+      </c>
+      <c r="BF58" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG58" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS58" t="n">
+      <c r="BH58" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI58" t="n">
         <v>207</v>
       </c>
-      <c r="AT58" t="n">
+      <c r="BJ58" t="n">
         <v>189</v>
       </c>
     </row>
@@ -9562,17 +12948,75 @@
         <v>66</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.6093453380549065</v>
-      </c>
-      <c r="AR59" t="inlineStr">
+        <v>1215.9</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>1226.18</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>1215.9</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>1182.15</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>1274.6</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>1318.63</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>102.73</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE59" t="inlineStr">
+        <is>
+          <t>Below ₹1182.15</t>
+        </is>
+      </c>
+      <c r="BF59" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG59" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS59" t="n">
+      <c r="BH59" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI59" t="n">
         <v>207</v>
       </c>
-      <c r="AT59" t="n">
+      <c r="BJ59" t="n">
         <v>189</v>
       </c>
     </row>
@@ -9716,17 +13160,75 @@
         <v>66</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.0756748538335015</v>
-      </c>
-      <c r="AR60" t="inlineStr">
+        <v>4192.04</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>4243.46</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>4192.04</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>4023.07</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>4485.9</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>4706.29</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>168.97</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>293.86</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>514.25</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE60" t="inlineStr">
+        <is>
+          <t>Below ₹4023.07</t>
+        </is>
+      </c>
+      <c r="BF60" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG60" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS60" t="n">
+      <c r="BH60" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI60" t="n">
         <v>207</v>
       </c>
-      <c r="AT60" t="n">
+      <c r="BJ60" t="n">
         <v>189</v>
       </c>
     </row>
@@ -9870,17 +13372,75 @@
         <v>66</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.1966097556938559</v>
-      </c>
-      <c r="AR61" t="inlineStr">
+        <v>579.5700000000001</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>586.02</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>579.5700000000001</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>558.35</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>616.46</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>644.13</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE61" t="inlineStr">
+        <is>
+          <t>Below ₹558.35</t>
+        </is>
+      </c>
+      <c r="BF61" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG61" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS61" t="n">
+      <c r="BH61" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI61" t="n">
         <v>207</v>
       </c>
-      <c r="AT61" t="n">
+      <c r="BJ61" t="n">
         <v>189</v>
       </c>
     </row>
@@ -10024,17 +13584,75 @@
         <v>64</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.1028685314284248</v>
-      </c>
-      <c r="AR62" t="inlineStr">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>100.81</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>107.44</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE62" t="inlineStr">
+        <is>
+          <t>Below ₹86.88</t>
+        </is>
+      </c>
+      <c r="BF62" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG62" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS62" t="n">
+      <c r="BH62" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI62" t="n">
         <v>304</v>
       </c>
-      <c r="AT62" t="n">
+      <c r="BJ62" t="n">
         <v>231</v>
       </c>
     </row>
@@ -10178,17 +13796,75 @@
         <v>64</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.2254098360655738</v>
-      </c>
-      <c r="AR63" t="inlineStr">
+        <v>12060.16</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>12202.86</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>12060.16</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>11591.29</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>12875.59</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>13487.16</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>468.87</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>815.4299999999999</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>1427</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE63" t="inlineStr">
+        <is>
+          <t>Below ₹11591.29</t>
+        </is>
+      </c>
+      <c r="BF63" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG63" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS63" t="n">
+      <c r="BH63" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI63" t="n">
         <v>304</v>
       </c>
-      <c r="AT63" t="n">
+      <c r="BJ63" t="n">
         <v>231</v>
       </c>
     </row>
@@ -10332,17 +14008,75 @@
         <v>64</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.09610150067312981</v>
-      </c>
-      <c r="AR64" t="inlineStr">
+        <v>130.35</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>132.57</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>130.35</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>123.05</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>143.04</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>152.56</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE64" t="inlineStr">
+        <is>
+          <t>Below ₹123.05</t>
+        </is>
+      </c>
+      <c r="BF64" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG64" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS64" t="n">
+      <c r="BH64" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI64" t="n">
         <v>304</v>
       </c>
-      <c r="AT64" t="n">
+      <c r="BJ64" t="n">
         <v>231</v>
       </c>
     </row>
@@ -10486,17 +14220,75 @@
         <v>64</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.04708222811671087</v>
-      </c>
-      <c r="AR65" t="inlineStr">
+        <v>6698.16</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>6801.21</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>6698.16</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>6359.57</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>7287.02</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>7728.66</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>338.59</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>588.86</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>1030.5</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE65" t="inlineStr">
+        <is>
+          <t>Below ₹6359.57</t>
+        </is>
+      </c>
+      <c r="BF65" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG65" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS65" t="n">
+      <c r="BH65" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI65" t="n">
         <v>304</v>
       </c>
-      <c r="AT65" t="n">
+      <c r="BJ65" t="n">
         <v>231</v>
       </c>
     </row>
@@ -10640,17 +14432,75 @@
         <v>64</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.1080645161290323</v>
-      </c>
-      <c r="AR66" t="inlineStr">
+        <v>22701.49</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>22879.96</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>22701.49</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>22115.07</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>23721.35</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>24486.24</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>586.42</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>1019.86</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>1784.75</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE66" t="inlineStr">
+        <is>
+          <t>Below ₹22115.07</t>
+        </is>
+      </c>
+      <c r="BF66" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG66" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS66" t="n">
+      <c r="BH66" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI66" t="n">
         <v>304</v>
       </c>
-      <c r="AT66" t="n">
+      <c r="BJ66" t="n">
         <v>231</v>
       </c>
     </row>
@@ -10794,17 +14644,75 @@
         <v>64</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.008756566489564967</v>
-      </c>
-      <c r="AR67" t="inlineStr">
+        <v>726.79</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>737.02</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>726.79</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>693.16</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>785.27</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>829.14</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE67" t="inlineStr">
+        <is>
+          <t>Below ₹693.16</t>
+        </is>
+      </c>
+      <c r="BF67" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG67" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS67" t="n">
+      <c r="BH67" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI67" t="n">
         <v>304</v>
       </c>
-      <c r="AT67" t="n">
+      <c r="BJ67" t="n">
         <v>231</v>
       </c>
     </row>
@@ -10948,17 +14856,75 @@
         <v>63</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.3297961176658163</v>
-      </c>
-      <c r="AR68" t="inlineStr">
+        <v>800.52</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>809.8</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>800.52</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>770.0599999999999</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>853.51</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>893.25</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>30.47</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE68" t="inlineStr">
+        <is>
+          <t>Below ₹770.06</t>
+        </is>
+      </c>
+      <c r="BF68" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG68" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS68" t="n">
+      <c r="BH68" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI68" t="n">
         <v>355</v>
       </c>
-      <c r="AT68" t="n">
+      <c r="BJ68" t="n">
         <v>309</v>
       </c>
     </row>
@@ -11102,17 +15068,75 @@
         <v>63</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.4592586564429013</v>
-      </c>
-      <c r="AR69" t="inlineStr">
+        <v>1723.04</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>1737.13</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>1723.04</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1676.74</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>1803.55</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>1863.94</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE69" t="inlineStr">
+        <is>
+          <t>Below ₹1676.74</t>
+        </is>
+      </c>
+      <c r="BF69" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG69" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS69" t="n">
+      <c r="BH69" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI69" t="n">
         <v>355</v>
       </c>
-      <c r="AT69" t="n">
+      <c r="BJ69" t="n">
         <v>309</v>
       </c>
     </row>
@@ -11256,17 +15280,75 @@
         <v>63</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.1239480542769203</v>
-      </c>
-      <c r="AR70" t="inlineStr">
+        <v>619.41</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>625.26</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>619.41</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>600.1799999999999</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>652.86</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>677.95</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE70" t="inlineStr">
+        <is>
+          <t>Below ₹600.18</t>
+        </is>
+      </c>
+      <c r="BF70" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG70" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS70" t="n">
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI70" t="n">
         <v>355</v>
       </c>
-      <c r="AT70" t="n">
+      <c r="BJ70" t="n">
         <v>309</v>
       </c>
     </row>
@@ -11410,17 +15492,75 @@
         <v>63</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.6845238095238095</v>
-      </c>
-      <c r="AR71" t="inlineStr">
+        <v>24327.77</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>24567.57</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>24327.77</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>23539.86</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>25698.06</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>26725.77</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>787.91</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>1370.29</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>2398</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE71" t="inlineStr">
+        <is>
+          <t>Below ₹23539.86</t>
+        </is>
+      </c>
+      <c r="BF71" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG71" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS71" t="n">
+      <c r="BH71" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI71" t="n">
         <v>355</v>
       </c>
-      <c r="AT71" t="n">
+      <c r="BJ71" t="n">
         <v>309</v>
       </c>
     </row>
@@ -11564,17 +15704,75 @@
         <v>63</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.2013654792066472</v>
-      </c>
-      <c r="AR72" t="inlineStr">
+        <v>405.67</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>412.58</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>405.67</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>445.2</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>474.85</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE72" t="inlineStr">
+        <is>
+          <t>Below ₹382.93</t>
+        </is>
+      </c>
+      <c r="BF72" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG72" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS72" t="n">
+      <c r="BH72" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI72" t="n">
         <v>355</v>
       </c>
-      <c r="AT72" t="n">
+      <c r="BJ72" t="n">
         <v>309</v>
       </c>
     </row>
@@ -11718,17 +15916,75 @@
         <v>61</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.08088235294117647</v>
-      </c>
-      <c r="AR73" t="inlineStr">
+        <v>828.79</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>839.95</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>828.79</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>792.09</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>892.6</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>940.46</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>111.68</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE73" t="inlineStr">
+        <is>
+          <t>Below ₹792.09</t>
+        </is>
+      </c>
+      <c r="BF73" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG73" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS73" t="n">
+      <c r="BH73" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI73" t="n">
         <v>445</v>
       </c>
-      <c r="AT73" t="n">
+      <c r="BJ73" t="n">
         <v>380</v>
       </c>
     </row>
@@ -11872,17 +16128,75 @@
         <v>61</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.02201473014304648</v>
-      </c>
-      <c r="AR74" t="inlineStr">
+        <v>731.23</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>743.66</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>731.23</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>690.38</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>802.26</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>855.54</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>124.31</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE74" t="inlineStr">
+        <is>
+          <t>Below ₹690.38</t>
+        </is>
+      </c>
+      <c r="BF74" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG74" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS74" t="n">
+      <c r="BH74" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI74" t="n">
         <v>445</v>
       </c>
-      <c r="AT74" t="n">
+      <c r="BJ74" t="n">
         <v>380</v>
       </c>
     </row>
@@ -12026,17 +16340,75 @@
         <v>61</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.1234516336096472</v>
-      </c>
-      <c r="AR75" t="inlineStr">
+        <v>669.01</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>677.2</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>669.01</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>642.09</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>715.83</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>750.9400000000001</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>81.93000000000001</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE75" t="inlineStr">
+        <is>
+          <t>Below ₹642.09</t>
+        </is>
+      </c>
+      <c r="BF75" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG75" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS75" t="n">
+      <c r="BH75" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI75" t="n">
         <v>445</v>
       </c>
-      <c r="AT75" t="n">
+      <c r="BJ75" t="n">
         <v>380</v>
       </c>
     </row>
@@ -12180,17 +16552,75 @@
         <v>61</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.2289803220035778</v>
-      </c>
-      <c r="AR76" t="inlineStr">
+        <v>1207.32</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>1224.64</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>1207.32</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1150.42</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>1306.28</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>173.18</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE76" t="inlineStr">
+        <is>
+          <t>Below ₹1150.42</t>
+        </is>
+      </c>
+      <c r="BF76" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG76" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS76" t="n">
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI76" t="n">
         <v>445</v>
       </c>
-      <c r="AT76" t="n">
+      <c r="BJ76" t="n">
         <v>380</v>
       </c>
     </row>
@@ -12334,17 +16764,75 @@
         <v>61</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.08477461965460527</v>
-      </c>
-      <c r="AR77" t="inlineStr">
+        <v>2379.1</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>2407.1</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>2379.1</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>2287.11</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>2539.08</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>2659.07</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>279.98</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE77" t="inlineStr">
+        <is>
+          <t>Below ₹2287.11</t>
+        </is>
+      </c>
+      <c r="BF77" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG77" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS77" t="n">
+      <c r="BH77" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI77" t="n">
         <v>445</v>
       </c>
-      <c r="AT77" t="n">
+      <c r="BJ77" t="n">
         <v>380</v>
       </c>
     </row>
@@ -12486,17 +16974,75 @@
         <v>60</v>
       </c>
       <c r="AQ78" t="n">
-        <v>-0.0593584185721464</v>
-      </c>
-      <c r="AR78" t="inlineStr">
+        <v>352.17</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>358.79</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>352.17</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>418.42</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr">
+        <is>
+          <t>Below ₹330.40</t>
+        </is>
+      </c>
+      <c r="BF78" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG78" t="inlineStr">
         <is>
           <t>Strong price trend | Breakout requires volume confirmation | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS78" t="n">
+      <c r="BH78" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI78" t="n">
         <v>493</v>
       </c>
-      <c r="AT78" t="n">
+      <c r="BJ78" t="n">
         <v>444</v>
       </c>
     </row>
@@ -12640,17 +17186,75 @@
         <v>60</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.08095598598591533</v>
-      </c>
-      <c r="AR79" t="inlineStr">
+        <v>49.58</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr">
+        <is>
+          <t>Below ₹48.05</t>
+        </is>
+      </c>
+      <c r="BF79" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG79" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS79" t="n">
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI79" t="n">
         <v>493</v>
       </c>
-      <c r="AT79" t="n">
+      <c r="BJ79" t="n">
         <v>444</v>
       </c>
     </row>
@@ -12794,17 +17398,75 @@
         <v>60</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.2143987341772152</v>
-      </c>
-      <c r="AR80" t="inlineStr">
+        <v>10592.14</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>10704.46</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>10592.14</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>10223.07</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>11234</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>11715.39</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>369.07</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>641.86</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>1123.25</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE80" t="inlineStr">
+        <is>
+          <t>Below ₹10223.07</t>
+        </is>
+      </c>
+      <c r="BF80" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG80" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS80" t="n">
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI80" t="n">
         <v>493</v>
       </c>
-      <c r="AT80" t="n">
+      <c r="BJ80" t="n">
         <v>444</v>
       </c>
     </row>
@@ -12946,17 +17608,75 @@
         <v>57</v>
       </c>
       <c r="AQ81" t="n">
-        <v>-0.04921967000807589</v>
-      </c>
-      <c r="AR81" t="inlineStr">
+        <v>21.4</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE81" t="inlineStr">
+        <is>
+          <t>Below ₹21.00</t>
+        </is>
+      </c>
+      <c r="BF81" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG81" t="inlineStr">
         <is>
           <t>Strong price trend | Breakout requires volume confirmation | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS81" t="n">
+      <c r="BH81" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI81" t="n">
         <v>565</v>
       </c>
-      <c r="AT81" t="n">
+      <c r="BJ81" t="n">
         <v>549</v>
       </c>
     </row>
@@ -13098,17 +17818,75 @@
         <v>57</v>
       </c>
       <c r="AQ82" t="n">
-        <v>-0.1663868153821396</v>
-      </c>
-      <c r="AR82" t="inlineStr">
+        <v>21.44</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE82" t="inlineStr">
+        <is>
+          <t>Below ₹20.95</t>
+        </is>
+      </c>
+      <c r="BF82" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG82" t="inlineStr">
         <is>
           <t>Strong price trend | Breakout requires volume confirmation | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS82" t="n">
+      <c r="BH82" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI82" t="n">
         <v>565</v>
       </c>
-      <c r="AT82" t="n">
+      <c r="BJ82" t="n">
         <v>549</v>
       </c>
     </row>
@@ -13252,17 +18030,75 @@
         <v>57</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.1068703579351245</v>
-      </c>
-      <c r="AR83" t="inlineStr">
+        <v>857.85</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>871.5</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>857.85</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>812.99</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>935.87</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>994.38</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>136.53</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE83" t="inlineStr">
+        <is>
+          <t>Below ₹812.99</t>
+        </is>
+      </c>
+      <c r="BF83" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG83" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS83" t="n">
+      <c r="BH83" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI83" t="n">
         <v>565</v>
       </c>
-      <c r="AT83" t="n">
+      <c r="BJ83" t="n">
         <v>549</v>
       </c>
     </row>
@@ -13406,17 +18242,75 @@
         <v>57</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.1509220323575331</v>
-      </c>
-      <c r="AR84" t="inlineStr">
+        <v>1248.87</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>1265.61</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>1248.87</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>1193.87</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>1344.53</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>1416.27</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>95.66</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE84" t="inlineStr">
+        <is>
+          <t>Below ₹1193.87</t>
+        </is>
+      </c>
+      <c r="BF84" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG84" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS84" t="n">
+      <c r="BH84" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI84" t="n">
         <v>565</v>
       </c>
-      <c r="AT84" t="n">
+      <c r="BJ84" t="n">
         <v>549</v>
       </c>
     </row>
@@ -13558,17 +18452,75 @@
         <v>54</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR85" t="inlineStr">
+        <v>145.77</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>145.73</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>145.77</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>146.76</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE85" t="inlineStr">
+        <is>
+          <t>Below ₹144.99</t>
+        </is>
+      </c>
+      <c r="BF85" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BG85" t="inlineStr">
         <is>
           <t>Strong price trend | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS85" t="n">
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI85" t="n">
         <v>638</v>
       </c>
-      <c r="AT85" t="n">
+      <c r="BJ85" t="n">
         <v>631</v>
       </c>
     </row>
